--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_shipbuilding_marine.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08989338340509831</v>
+        <v>0.08974959663828812</v>
       </c>
       <c r="C2">
-        <v>1047.309120684754</v>
+        <v>1039.144243136935</v>
       </c>
       <c r="D2">
-        <v>776.4091206847544</v>
+        <v>778.9492431369351</v>
       </c>
       <c r="E2">
-        <v>-377.2</v>
+        <v>-366.495</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.705</v>
       </c>
       <c r="G2">
         <v>270.9</v>
@@ -1445,28 +1445,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5384614999999999</v>
       </c>
       <c r="N2">
-        <v>194.1666666666667</v>
+        <v>193.6282051666667</v>
       </c>
       <c r="O2">
-        <v>38.83333333333334</v>
+        <v>38.72564103333334</v>
       </c>
       <c r="P2">
-        <v>155.3333333333333</v>
+        <v>154.9025641333333</v>
       </c>
       <c r="Q2">
-        <v>213.3333333333334</v>
+        <v>212.9025641333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08989338340509831</v>
+        <v>0.0902496935740284</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367392</v>
+        <v>0.8664072619289553</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>360.5952638520427</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08974959663828812</v>
+        <v>0.08960580987147793</v>
       </c>
       <c r="C3">
-        <v>1039.144243136935</v>
+        <v>1030.996040819902</v>
       </c>
       <c r="D3">
-        <v>778.9492431369351</v>
+        <v>781.5060408199025</v>
       </c>
       <c r="E3">
-        <v>-366.495</v>
+        <v>-355.79</v>
       </c>
       <c r="F3">
-        <v>10.705</v>
+        <v>21.41</v>
       </c>
       <c r="G3">
         <v>270.9</v>
@@ -1527,28 +1527,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M3">
-        <v>0.5384614999999999</v>
+        <v>1.076923</v>
       </c>
       <c r="N3">
-        <v>193.6282051666667</v>
+        <v>193.0897436666667</v>
       </c>
       <c r="O3">
-        <v>38.72564103333334</v>
+        <v>38.61794873333334</v>
       </c>
       <c r="P3">
-        <v>154.9025641333333</v>
+        <v>154.4717949333333</v>
       </c>
       <c r="Q3">
-        <v>212.9025641333333</v>
+        <v>212.4717949333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0902496935740284</v>
+        <v>0.09061327537905911</v>
       </c>
       <c r="T3">
-        <v>0.8664072619289553</v>
+        <v>0.8734941480434615</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>360.5952638520427</v>
+        <v>180.2976319260214</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08960580987147793</v>
+        <v>0.08946202310466772</v>
       </c>
       <c r="C4">
-        <v>1030.996040819902</v>
+        <v>1022.864678477112</v>
       </c>
       <c r="D4">
-        <v>781.5060408199025</v>
+        <v>784.0796784771123</v>
       </c>
       <c r="E4">
-        <v>-355.79</v>
+        <v>-345.085</v>
       </c>
       <c r="F4">
-        <v>21.41</v>
+        <v>32.115</v>
       </c>
       <c r="G4">
         <v>270.9</v>
@@ -1609,28 +1609,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M4">
-        <v>1.076923</v>
+        <v>1.6153845</v>
       </c>
       <c r="N4">
-        <v>193.0897436666667</v>
+        <v>192.5512821666667</v>
       </c>
       <c r="O4">
-        <v>38.61794873333334</v>
+        <v>38.51025643333334</v>
       </c>
       <c r="P4">
-        <v>154.4717949333333</v>
+        <v>154.0410257333334</v>
       </c>
       <c r="Q4">
-        <v>212.4717949333333</v>
+        <v>212.0410257333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09061327537905911</v>
+        <v>0.09098435371615228</v>
       </c>
       <c r="T4">
-        <v>0.8734941480434615</v>
+        <v>0.8807271555211532</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>180.2976319260214</v>
+        <v>120.1984212840142</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08946202310466772</v>
+        <v>0.08931823633785753</v>
       </c>
       <c r="C5">
-        <v>1022.864678477112</v>
+        <v>1014.750323029307</v>
       </c>
       <c r="D5">
-        <v>784.0796784771123</v>
+        <v>786.6703230293072</v>
       </c>
       <c r="E5">
-        <v>-345.085</v>
+        <v>-334.38</v>
       </c>
       <c r="F5">
-        <v>32.115</v>
+        <v>42.82</v>
       </c>
       <c r="G5">
         <v>270.9</v>
@@ -1691,28 +1691,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M5">
-        <v>1.6153845</v>
+        <v>2.153846</v>
       </c>
       <c r="N5">
-        <v>192.5512821666667</v>
+        <v>192.0128206666667</v>
       </c>
       <c r="O5">
-        <v>38.51025643333334</v>
+        <v>38.40256413333334</v>
       </c>
       <c r="P5">
-        <v>154.0410257333334</v>
+        <v>153.6102565333334</v>
       </c>
       <c r="Q5">
-        <v>212.0410257333334</v>
+        <v>211.6102565333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09098435371615228</v>
+        <v>0.09136316285193492</v>
       </c>
       <c r="T5">
-        <v>0.8807271555211532</v>
+        <v>0.8881108506546306</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>120.1984212840142</v>
+        <v>90.14881596301069</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08931823633785753</v>
+        <v>0.08917444957104732</v>
       </c>
       <c r="C6">
-        <v>1014.750323029307</v>
+        <v>1006.653143610607</v>
       </c>
       <c r="D6">
-        <v>786.6703230293072</v>
+        <v>789.278143610607</v>
       </c>
       <c r="E6">
-        <v>-334.38</v>
+        <v>-323.675</v>
       </c>
       <c r="F6">
-        <v>42.82</v>
+        <v>53.52500000000001</v>
       </c>
       <c r="G6">
         <v>270.9</v>
@@ -1773,28 +1773,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M6">
-        <v>2.153846</v>
+        <v>2.6923075</v>
       </c>
       <c r="N6">
-        <v>192.0128206666667</v>
+        <v>191.4743591666667</v>
       </c>
       <c r="O6">
-        <v>38.40256413333334</v>
+        <v>38.29487183333334</v>
       </c>
       <c r="P6">
-        <v>153.6102565333334</v>
+        <v>153.1794873333334</v>
       </c>
       <c r="Q6">
-        <v>211.6102565333334</v>
+        <v>211.1794873333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09136316285193492</v>
+        <v>0.09174994691689192</v>
       </c>
       <c r="T6">
-        <v>0.8881108506546306</v>
+        <v>0.8956499920014439</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>90.14881596301069</v>
+        <v>72.11905277040853</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08917444957104732</v>
+        <v>0.08903066280423712</v>
       </c>
       <c r="C7">
-        <v>1006.653143610607</v>
+        <v>998.5733116053157</v>
       </c>
       <c r="D7">
-        <v>789.278143610607</v>
+        <v>791.9033116053157</v>
       </c>
       <c r="E7">
-        <v>-323.675</v>
+        <v>-312.97</v>
       </c>
       <c r="F7">
-        <v>53.52500000000001</v>
+        <v>64.23</v>
       </c>
       <c r="G7">
         <v>270.9</v>
@@ -1855,28 +1855,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M7">
-        <v>2.6923075</v>
+        <v>3.230769</v>
       </c>
       <c r="N7">
-        <v>191.4743591666667</v>
+        <v>190.9358976666667</v>
       </c>
       <c r="O7">
-        <v>38.29487183333334</v>
+        <v>38.18717953333334</v>
       </c>
       <c r="P7">
-        <v>153.1794873333334</v>
+        <v>152.7487181333333</v>
       </c>
       <c r="Q7">
-        <v>211.1794873333334</v>
+        <v>210.7487181333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09174994691689192</v>
+        <v>0.0921449604300395</v>
       </c>
       <c r="T7">
-        <v>0.8956499920014439</v>
+        <v>0.9033495406109557</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>72.11905277040853</v>
+        <v>60.09921064200712</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08903066280423712</v>
+        <v>0.08888687603742694</v>
       </c>
       <c r="C8">
-        <v>998.5733116053157</v>
+        <v>990.5110006854684</v>
       </c>
       <c r="D8">
-        <v>791.9033116053157</v>
+        <v>794.5460006854685</v>
       </c>
       <c r="E8">
-        <v>-312.97</v>
+        <v>-302.265</v>
       </c>
       <c r="F8">
-        <v>64.23</v>
+        <v>74.93499999999999</v>
       </c>
       <c r="G8">
         <v>270.9</v>
@@ -1937,28 +1937,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M8">
-        <v>3.230769</v>
+        <v>3.769230499999999</v>
       </c>
       <c r="N8">
-        <v>190.9358976666667</v>
+        <v>190.3974361666667</v>
       </c>
       <c r="O8">
-        <v>38.18717953333334</v>
+        <v>38.07948723333334</v>
       </c>
       <c r="P8">
-        <v>152.7487181333333</v>
+        <v>152.3179489333334</v>
       </c>
       <c r="Q8">
-        <v>210.7487181333333</v>
+        <v>210.3179489333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0921449604300395</v>
+        <v>0.09254846885744833</v>
       </c>
       <c r="T8">
-        <v>0.9033495406109557</v>
+        <v>0.9112146709109945</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>60.09921064200712</v>
+        <v>51.5136091217204</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08888687603742694</v>
+        <v>0.08874308927061675</v>
       </c>
       <c r="C9">
-        <v>990.5110006854684</v>
+        <v>982.4663868491324</v>
       </c>
       <c r="D9">
-        <v>794.5460006854685</v>
+        <v>797.2063868491323</v>
       </c>
       <c r="E9">
-        <v>-302.265</v>
+        <v>-291.56</v>
       </c>
       <c r="F9">
-        <v>74.935</v>
+        <v>85.64</v>
       </c>
       <c r="G9">
         <v>270.9</v>
@@ -2019,28 +2019,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M9">
-        <v>3.7692305</v>
+        <v>4.307691999999999</v>
       </c>
       <c r="N9">
-        <v>190.3974361666667</v>
+        <v>189.8589746666667</v>
       </c>
       <c r="O9">
-        <v>38.07948723333334</v>
+        <v>37.97179493333334</v>
       </c>
       <c r="P9">
-        <v>152.3179489333334</v>
+        <v>151.8871797333333</v>
       </c>
       <c r="Q9">
-        <v>210.3179489333334</v>
+        <v>209.8871797333334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09254846885744833</v>
+        <v>0.09296074920719211</v>
       </c>
       <c r="T9">
-        <v>0.9112146709109945</v>
+        <v>0.9192507823045124</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>51.51360912172039</v>
+        <v>45.07440798150534</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08874308927061675</v>
+        <v>0.08859930250380654</v>
       </c>
       <c r="C10">
-        <v>982.4663868491324</v>
+        <v>974.4396484594772</v>
       </c>
       <c r="D10">
-        <v>797.2063868491323</v>
+        <v>799.8846484594773</v>
       </c>
       <c r="E10">
-        <v>-291.56</v>
+        <v>-280.855</v>
       </c>
       <c r="F10">
-        <v>85.64</v>
+        <v>96.345</v>
       </c>
       <c r="G10">
         <v>270.9</v>
@@ -2101,28 +2101,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M10">
-        <v>4.307691999999999</v>
+        <v>4.8461535</v>
       </c>
       <c r="N10">
-        <v>189.8589746666667</v>
+        <v>189.3205131666667</v>
       </c>
       <c r="O10">
-        <v>37.97179493333334</v>
+        <v>37.86410263333334</v>
       </c>
       <c r="P10">
-        <v>151.8871797333333</v>
+        <v>151.4564105333333</v>
       </c>
       <c r="Q10">
-        <v>209.8871797333334</v>
+        <v>209.4564105333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09296074920719211</v>
+        <v>0.09338209066352367</v>
       </c>
       <c r="T10">
-        <v>0.9192507823045124</v>
+        <v>0.9274635115308547</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>45.07440798150534</v>
+        <v>40.06614042800474</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08859930250380654</v>
+        <v>0.08845551573699635</v>
       </c>
       <c r="C11">
-        <v>974.4396484594772</v>
+        <v>966.4309662846381</v>
       </c>
       <c r="D11">
-        <v>799.8846484594773</v>
+        <v>802.5809662846381</v>
       </c>
       <c r="E11">
-        <v>-280.855</v>
+        <v>-270.15</v>
       </c>
       <c r="F11">
-        <v>96.345</v>
+        <v>107.05</v>
       </c>
       <c r="G11">
         <v>270.9</v>
@@ -2183,28 +2183,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M11">
-        <v>4.8461535</v>
+        <v>5.384614999999999</v>
       </c>
       <c r="N11">
-        <v>189.3205131666667</v>
+        <v>188.7820516666667</v>
       </c>
       <c r="O11">
-        <v>37.86410263333334</v>
+        <v>37.75641033333334</v>
       </c>
       <c r="P11">
-        <v>151.4564105333333</v>
+        <v>151.0256413333333</v>
       </c>
       <c r="Q11">
-        <v>209.4564105333333</v>
+        <v>209.0256413333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09338209066352367</v>
+        <v>0.09381279526332928</v>
       </c>
       <c r="T11">
-        <v>0.9274635115308547</v>
+        <v>0.9358587458511159</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>40.06614042800474</v>
+        <v>36.05952638520427</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08845551573699635</v>
+        <v>0.08831172897018615</v>
       </c>
       <c r="C12">
-        <v>966.4309662846381</v>
+        <v>958.4405235383882</v>
       </c>
       <c r="D12">
-        <v>802.5809662846381</v>
+        <v>805.2955235383882</v>
       </c>
       <c r="E12">
-        <v>-270.15</v>
+        <v>-259.445</v>
       </c>
       <c r="F12">
-        <v>107.05</v>
+        <v>117.755</v>
       </c>
       <c r="G12">
         <v>270.9</v>
@@ -2265,28 +2265,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M12">
-        <v>5.384615</v>
+        <v>5.9230765</v>
       </c>
       <c r="N12">
-        <v>188.7820516666667</v>
+        <v>188.2435901666667</v>
       </c>
       <c r="O12">
-        <v>37.75641033333334</v>
+        <v>37.64871803333334</v>
       </c>
       <c r="P12">
-        <v>151.0256413333333</v>
+        <v>150.5948721333334</v>
       </c>
       <c r="Q12">
-        <v>209.0256413333333</v>
+        <v>208.5948721333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09381279526332928</v>
+        <v>0.09425317861818668</v>
       </c>
       <c r="T12">
-        <v>0.9358587458511161</v>
+        <v>0.9444426371223942</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>36.05952638520427</v>
+        <v>32.78138762291297</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08831172897018615</v>
+        <v>0.08816794220337595</v>
       </c>
       <c r="C13">
-        <v>958.4405235383882</v>
+        <v>950.4685059216363</v>
       </c>
       <c r="D13">
-        <v>805.2955235383882</v>
+        <v>808.0285059216363</v>
       </c>
       <c r="E13">
-        <v>-259.445</v>
+        <v>-248.74</v>
       </c>
       <c r="F13">
-        <v>117.755</v>
+        <v>128.46</v>
       </c>
       <c r="G13">
         <v>270.9</v>
@@ -2347,28 +2347,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M13">
-        <v>5.9230765</v>
+        <v>6.461538</v>
       </c>
       <c r="N13">
-        <v>188.2435901666667</v>
+        <v>187.7051286666667</v>
       </c>
       <c r="O13">
-        <v>37.64871803333334</v>
+        <v>37.54102573333334</v>
       </c>
       <c r="P13">
-        <v>150.5948721333334</v>
+        <v>150.1641029333334</v>
       </c>
       <c r="Q13">
-        <v>208.5948721333334</v>
+        <v>208.1641029333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09425317861818668</v>
+        <v>0.09470357068565449</v>
       </c>
       <c r="T13">
-        <v>0.9444426371223942</v>
+        <v>0.9532216168316562</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.78138762291297</v>
+        <v>30.04960532100356</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08816794220337595</v>
+        <v>0.08802415543656576</v>
       </c>
       <c r="C14">
-        <v>950.4685059216363</v>
+        <v>942.5151016647767</v>
       </c>
       <c r="D14">
-        <v>808.0285059216363</v>
+        <v>810.7801016647767</v>
       </c>
       <c r="E14">
-        <v>-248.74</v>
+        <v>-238.035</v>
       </c>
       <c r="F14">
-        <v>128.46</v>
+        <v>139.165</v>
       </c>
       <c r="G14">
         <v>270.9</v>
@@ -2429,28 +2429,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M14">
-        <v>6.461538</v>
+        <v>6.999999499999999</v>
       </c>
       <c r="N14">
-        <v>187.7051286666667</v>
+        <v>187.1666671666667</v>
       </c>
       <c r="O14">
-        <v>37.54102573333334</v>
+        <v>37.43333343333334</v>
       </c>
       <c r="P14">
-        <v>150.1641029333334</v>
+        <v>149.7333337333334</v>
       </c>
       <c r="Q14">
-        <v>208.1641029333334</v>
+        <v>207.7333337333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09470357068565449</v>
+        <v>0.09516431659375374</v>
       </c>
       <c r="T14">
-        <v>0.9532216168316562</v>
+        <v>0.9622024121664183</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>30.04960532100356</v>
+        <v>27.7380972193879</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08802415543656576</v>
+        <v>0.08788036866975557</v>
       </c>
       <c r="C15">
-        <v>942.5151016647767</v>
+        <v>934.5805015709019</v>
       </c>
       <c r="D15">
-        <v>810.7801016647767</v>
+        <v>813.550501570902</v>
       </c>
       <c r="E15">
-        <v>-238.035</v>
+        <v>-227.33</v>
       </c>
       <c r="F15">
-        <v>139.165</v>
+        <v>149.87</v>
       </c>
       <c r="G15">
         <v>270.9</v>
@@ -2511,28 +2511,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M15">
-        <v>6.999999499999999</v>
+        <v>7.538461</v>
       </c>
       <c r="N15">
-        <v>187.1666671666667</v>
+        <v>186.6282056666667</v>
       </c>
       <c r="O15">
-        <v>37.43333343333334</v>
+        <v>37.32564113333333</v>
       </c>
       <c r="P15">
-        <v>149.7333337333334</v>
+        <v>149.3025645333333</v>
       </c>
       <c r="Q15">
-        <v>207.7333337333334</v>
+        <v>207.3025645333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09516431659375374</v>
+        <v>0.09563577752297159</v>
       </c>
       <c r="T15">
-        <v>0.9622024121664183</v>
+        <v>0.9713920632066402</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.7380972193879</v>
+        <v>25.75680456086019</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08788036866975557</v>
+        <v>0.08773658190294537</v>
       </c>
       <c r="C16">
-        <v>934.5805015709019</v>
+        <v>926.6648990599112</v>
       </c>
       <c r="D16">
-        <v>813.550501570902</v>
+        <v>816.3398990599112</v>
       </c>
       <c r="E16">
-        <v>-227.33</v>
+        <v>-216.625</v>
       </c>
       <c r="F16">
-        <v>149.87</v>
+        <v>160.575</v>
       </c>
       <c r="G16">
         <v>270.9</v>
@@ -2593,28 +2593,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M16">
-        <v>7.538461</v>
+        <v>8.0769225</v>
       </c>
       <c r="N16">
-        <v>186.6282056666667</v>
+        <v>186.0897441666667</v>
       </c>
       <c r="O16">
-        <v>37.32564113333333</v>
+        <v>37.21794883333334</v>
       </c>
       <c r="P16">
-        <v>149.3025645333333</v>
+        <v>148.8717953333334</v>
       </c>
       <c r="Q16">
-        <v>207.3025645333333</v>
+        <v>206.8717953333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09563577752297159</v>
+        <v>0.09611833165052396</v>
       </c>
       <c r="T16">
-        <v>0.9713920632066402</v>
+        <v>0.9807979413301612</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.75680456086019</v>
+        <v>24.03968425680285</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08773658190294537</v>
+        <v>0.08759279513613516</v>
       </c>
       <c r="C17">
-        <v>926.6648990599112</v>
+        <v>918.7684902135213</v>
       </c>
       <c r="D17">
-        <v>816.3398990599112</v>
+        <v>819.1484902135214</v>
       </c>
       <c r="E17">
-        <v>-216.625</v>
+        <v>-205.92</v>
       </c>
       <c r="F17">
-        <v>160.575</v>
+        <v>171.28</v>
       </c>
       <c r="G17">
         <v>270.9</v>
@@ -2675,28 +2675,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M17">
-        <v>8.076922499999998</v>
+        <v>8.615383999999999</v>
       </c>
       <c r="N17">
-        <v>186.0897441666667</v>
+        <v>185.5512826666667</v>
       </c>
       <c r="O17">
-        <v>37.21794883333334</v>
+        <v>37.11025653333333</v>
       </c>
       <c r="P17">
-        <v>148.8717953333334</v>
+        <v>148.4410261333333</v>
       </c>
       <c r="Q17">
-        <v>206.8717953333334</v>
+        <v>206.4410261333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09611833165052396</v>
+        <v>0.09661237516206567</v>
       </c>
       <c r="T17">
-        <v>0.9807979413301612</v>
+        <v>0.9904277689328136</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.03968425680285</v>
+        <v>22.53720399075267</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08759279513613516</v>
+        <v>0.08744900836932497</v>
       </c>
       <c r="C18">
-        <v>918.7684902135213</v>
+        <v>910.8914738212176</v>
       </c>
       <c r="D18">
-        <v>819.1484902135214</v>
+        <v>821.9764738212177</v>
       </c>
       <c r="E18">
-        <v>-205.92</v>
+        <v>-195.215</v>
       </c>
       <c r="F18">
-        <v>171.28</v>
+        <v>181.985</v>
       </c>
       <c r="G18">
         <v>270.9</v>
@@ -2757,28 +2757,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M18">
-        <v>8.615383999999999</v>
+        <v>9.153845500000001</v>
       </c>
       <c r="N18">
-        <v>185.5512826666667</v>
+        <v>185.0128211666667</v>
       </c>
       <c r="O18">
-        <v>37.11025653333333</v>
+        <v>37.00256423333334</v>
       </c>
       <c r="P18">
-        <v>148.4410261333333</v>
+        <v>148.0102569333334</v>
       </c>
       <c r="Q18">
-        <v>206.4410261333334</v>
+        <v>206.0102569333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09661237516206567</v>
+        <v>0.09711832333653611</v>
       </c>
       <c r="T18">
-        <v>0.9904277689328136</v>
+        <v>1.000289640574084</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.53720399075267</v>
+        <v>21.21148610894369</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08744900836932497</v>
+        <v>0.08730522160251478</v>
       </c>
       <c r="C19">
-        <v>910.8914738212176</v>
+        <v>903.0340514271552</v>
       </c>
       <c r="D19">
-        <v>821.9764738212177</v>
+        <v>824.8240514271552</v>
       </c>
       <c r="E19">
-        <v>-195.215</v>
+        <v>-184.51</v>
       </c>
       <c r="F19">
-        <v>181.985</v>
+        <v>192.69</v>
       </c>
       <c r="G19">
         <v>270.9</v>
@@ -2839,28 +2839,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M19">
-        <v>9.153845500000001</v>
+        <v>9.692307000000001</v>
       </c>
       <c r="N19">
-        <v>185.0128211666667</v>
+        <v>184.4743596666667</v>
       </c>
       <c r="O19">
-        <v>37.00256423333334</v>
+        <v>36.89487193333334</v>
       </c>
       <c r="P19">
-        <v>148.0102569333334</v>
+        <v>147.5794877333333</v>
       </c>
       <c r="Q19">
-        <v>206.0102569333334</v>
+        <v>205.5794877333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09711832333653611</v>
+        <v>0.09763661171038387</v>
       </c>
       <c r="T19">
-        <v>1.000289640574084</v>
+        <v>1.01039204567002</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.21148610894369</v>
+        <v>20.03307021400237</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08730522160251479</v>
+        <v>0.0871614348357046</v>
       </c>
       <c r="C20">
-        <v>903.0340514271547</v>
+        <v>895.1964273780397</v>
       </c>
       <c r="D20">
-        <v>824.8240514271548</v>
+        <v>827.6914273780397</v>
       </c>
       <c r="E20">
-        <v>-184.51</v>
+        <v>-173.805</v>
       </c>
       <c r="F20">
-        <v>192.69</v>
+        <v>203.395</v>
       </c>
       <c r="G20">
         <v>270.9</v>
@@ -2921,28 +2921,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M20">
-        <v>9.692307</v>
+        <v>10.2307685</v>
       </c>
       <c r="N20">
-        <v>184.4743596666667</v>
+        <v>183.9358981666667</v>
       </c>
       <c r="O20">
-        <v>36.89487193333334</v>
+        <v>36.78717963333334</v>
       </c>
       <c r="P20">
-        <v>147.5794877333333</v>
+        <v>147.1487185333334</v>
       </c>
       <c r="Q20">
-        <v>205.5794877333333</v>
+        <v>205.1487185333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09763661171038387</v>
+        <v>0.09816769732803035</v>
       </c>
       <c r="T20">
-        <v>1.01039204567002</v>
+        <v>1.02074389286709</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.03307021400237</v>
+        <v>18.97869809747593</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0871614348357046</v>
+        <v>0.08701764806889438</v>
       </c>
       <c r="C21">
-        <v>895.1964273780397</v>
+        <v>887.3788088720129</v>
       </c>
       <c r="D21">
-        <v>827.6914273780397</v>
+        <v>830.578808872013</v>
       </c>
       <c r="E21">
-        <v>-173.805</v>
+        <v>-163.1</v>
       </c>
       <c r="F21">
-        <v>203.395</v>
+        <v>214.1</v>
       </c>
       <c r="G21">
         <v>270.9</v>
@@ -3003,28 +3003,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M21">
-        <v>10.2307685</v>
+        <v>10.76923</v>
       </c>
       <c r="N21">
-        <v>183.9358981666667</v>
+        <v>183.3974366666667</v>
       </c>
       <c r="O21">
-        <v>36.78717963333334</v>
+        <v>36.67948733333334</v>
       </c>
       <c r="P21">
-        <v>147.1487185333334</v>
+        <v>146.7179493333334</v>
       </c>
       <c r="Q21">
-        <v>205.1487185333334</v>
+        <v>204.7179493333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09816769732803035</v>
+        <v>0.09871206008611796</v>
       </c>
       <c r="T21">
-        <v>1.02074389286709</v>
+        <v>1.031354536244087</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.97869809747593</v>
+        <v>18.02976319260214</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08701764806889438</v>
+        <v>0.08687386130208417</v>
       </c>
       <c r="C22">
-        <v>887.3788088720129</v>
+        <v>879.5814060085577</v>
       </c>
       <c r="D22">
-        <v>830.578808872013</v>
+        <v>833.4864060085578</v>
       </c>
       <c r="E22">
-        <v>-163.1</v>
+        <v>-152.395</v>
       </c>
       <c r="F22">
-        <v>214.1</v>
+        <v>224.805</v>
       </c>
       <c r="G22">
         <v>270.9</v>
@@ -3085,28 +3085,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M22">
-        <v>10.76923</v>
+        <v>11.3076915</v>
       </c>
       <c r="N22">
-        <v>183.3974366666667</v>
+        <v>182.8589751666667</v>
       </c>
       <c r="O22">
-        <v>36.67948733333334</v>
+        <v>36.57179503333334</v>
       </c>
       <c r="P22">
-        <v>146.7179493333334</v>
+        <v>146.2871801333334</v>
       </c>
       <c r="Q22">
-        <v>204.7179493333334</v>
+        <v>204.2871801333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09871206008611796</v>
+        <v>0.09927020417985338</v>
       </c>
       <c r="T22">
-        <v>1.031354536244087</v>
+        <v>1.042233803504046</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.02976319260214</v>
+        <v>17.17120304057346</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08687386130208417</v>
+        <v>0.08673007453527398</v>
       </c>
       <c r="C23">
-        <v>879.5814060085578</v>
+        <v>871.8044318394643</v>
       </c>
       <c r="D23">
-        <v>833.4864060085578</v>
+        <v>836.4144318394643</v>
       </c>
       <c r="E23">
-        <v>-152.395</v>
+        <v>-141.69</v>
       </c>
       <c r="F23">
-        <v>224.805</v>
+        <v>235.51</v>
       </c>
       <c r="G23">
         <v>270.9</v>
@@ -3167,28 +3167,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M23">
-        <v>11.3076915</v>
+        <v>11.846153</v>
       </c>
       <c r="N23">
-        <v>182.8589751666667</v>
+        <v>182.3205136666667</v>
       </c>
       <c r="O23">
-        <v>36.57179503333334</v>
+        <v>36.46410273333334</v>
       </c>
       <c r="P23">
-        <v>146.2871801333334</v>
+        <v>145.8564109333334</v>
       </c>
       <c r="Q23">
-        <v>204.2871801333334</v>
+        <v>203.8564109333334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09927020417985338</v>
+        <v>0.09984265966060768</v>
       </c>
       <c r="T23">
-        <v>1.042233803504046</v>
+        <v>1.053392026334773</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.17120304057346</v>
+        <v>16.39069381145649</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08673007453527398</v>
+        <v>0.0865862877684638</v>
       </c>
       <c r="C24">
-        <v>871.8044318394643</v>
+        <v>864.048102420869</v>
       </c>
       <c r="D24">
-        <v>836.4144318394643</v>
+        <v>839.3631024208689</v>
       </c>
       <c r="E24">
-        <v>-141.69</v>
+        <v>-130.985</v>
       </c>
       <c r="F24">
-        <v>235.51</v>
+        <v>246.215</v>
       </c>
       <c r="G24">
         <v>270.9</v>
@@ -3249,28 +3249,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M24">
-        <v>11.846153</v>
+        <v>12.3846145</v>
       </c>
       <c r="N24">
-        <v>182.3205136666667</v>
+        <v>181.7820521666667</v>
       </c>
       <c r="O24">
-        <v>36.46410273333334</v>
+        <v>36.35641043333334</v>
       </c>
       <c r="P24">
-        <v>145.8564109333334</v>
+        <v>145.4256417333334</v>
       </c>
       <c r="Q24">
-        <v>203.8564109333334</v>
+        <v>203.4256417333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09984265966060768</v>
+        <v>0.100429984114888</v>
       </c>
       <c r="T24">
-        <v>1.053392026334773</v>
+        <v>1.064840073135129</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.39069381145649</v>
+        <v>15.67805495008881</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0865862877684638</v>
+        <v>0.0864425010016536</v>
       </c>
       <c r="C25">
-        <v>864.048102420869</v>
+        <v>856.3126368663984</v>
       </c>
       <c r="D25">
-        <v>839.3631024208689</v>
+        <v>842.3326368663984</v>
       </c>
       <c r="E25">
-        <v>-130.985</v>
+        <v>-120.28</v>
       </c>
       <c r="F25">
-        <v>246.215</v>
+        <v>256.92</v>
       </c>
       <c r="G25">
         <v>270.9</v>
@@ -3331,28 +3331,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M25">
-        <v>12.3846145</v>
+        <v>12.923076</v>
       </c>
       <c r="N25">
-        <v>181.7820521666667</v>
+        <v>181.2435906666667</v>
       </c>
       <c r="O25">
-        <v>36.35641043333334</v>
+        <v>36.24871813333333</v>
       </c>
       <c r="P25">
-        <v>145.4256417333334</v>
+        <v>144.9948725333333</v>
       </c>
       <c r="Q25">
-        <v>203.4256417333334</v>
+        <v>202.9948725333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.100429984114888</v>
+        <v>0.10103276447586</v>
       </c>
       <c r="T25">
-        <v>1.064840073135129</v>
+        <v>1.076589384324968</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.67805495008881</v>
+        <v>15.02480266050178</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0864425010016536</v>
+        <v>0.08629871423484339</v>
       </c>
       <c r="C26">
-        <v>856.3126368663984</v>
+        <v>848.5982574014456</v>
       </c>
       <c r="D26">
-        <v>842.3326368663984</v>
+        <v>845.3232574014456</v>
       </c>
       <c r="E26">
-        <v>-120.28</v>
+        <v>-109.575</v>
       </c>
       <c r="F26">
-        <v>256.92</v>
+        <v>267.625</v>
       </c>
       <c r="G26">
         <v>270.9</v>
@@ -3413,28 +3413,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M26">
-        <v>12.923076</v>
+        <v>13.4615375</v>
       </c>
       <c r="N26">
-        <v>181.2435906666667</v>
+        <v>180.7051291666667</v>
       </c>
       <c r="O26">
-        <v>36.24871813333333</v>
+        <v>36.14102583333334</v>
       </c>
       <c r="P26">
-        <v>144.9948725333333</v>
+        <v>144.5641033333333</v>
       </c>
       <c r="Q26">
-        <v>202.9948725333334</v>
+        <v>202.5641033333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.10103276447586</v>
+        <v>0.1016516189797912</v>
       </c>
       <c r="T26">
-        <v>1.076589384324968</v>
+        <v>1.08865201047987</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.02480266050178</v>
+        <v>14.42381055408171</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08629871423484339</v>
+        <v>0.0861549274680332</v>
       </c>
       <c r="C27">
-        <v>848.5982574014456</v>
+        <v>840.9051894186077</v>
       </c>
       <c r="D27">
-        <v>845.3232574014456</v>
+        <v>848.3351894186077</v>
       </c>
       <c r="E27">
-        <v>-109.575</v>
+        <v>-98.87</v>
       </c>
       <c r="F27">
-        <v>267.625</v>
+        <v>278.33</v>
       </c>
       <c r="G27">
         <v>270.9</v>
@@ -3495,28 +3495,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M27">
-        <v>13.4615375</v>
+        <v>13.999999</v>
       </c>
       <c r="N27">
-        <v>180.7051291666667</v>
+        <v>180.1666676666667</v>
       </c>
       <c r="O27">
-        <v>36.14102583333334</v>
+        <v>36.03333353333334</v>
       </c>
       <c r="P27">
-        <v>144.5641033333333</v>
+        <v>144.1333341333333</v>
       </c>
       <c r="Q27">
-        <v>202.5641033333334</v>
+        <v>202.1333341333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1016516189797912</v>
+        <v>0.102287199281126</v>
       </c>
       <c r="T27">
-        <v>1.08865201047987</v>
+        <v>1.101040653557877</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.42381055408171</v>
+        <v>13.86904860969395</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0861549274680332</v>
+        <v>0.08601114070122301</v>
       </c>
       <c r="C28">
-        <v>840.9051894186077</v>
+        <v>833.2336615343115</v>
       </c>
       <c r="D28">
-        <v>848.3351894186077</v>
+        <v>851.3686615343116</v>
       </c>
       <c r="E28">
-        <v>-98.87</v>
+        <v>-88.16499999999996</v>
       </c>
       <c r="F28">
-        <v>278.33</v>
+        <v>289.035</v>
       </c>
       <c r="G28">
         <v>270.9</v>
@@ -3577,28 +3577,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M28">
-        <v>13.999999</v>
+        <v>14.5384605</v>
       </c>
       <c r="N28">
-        <v>180.1666676666667</v>
+        <v>179.6282061666667</v>
       </c>
       <c r="O28">
-        <v>36.03333353333334</v>
+        <v>35.92564123333334</v>
       </c>
       <c r="P28">
-        <v>144.1333341333333</v>
+        <v>143.7025649333333</v>
       </c>
       <c r="Q28">
-        <v>202.1333341333333</v>
+        <v>201.7025649333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.102287199281126</v>
+        <v>0.1029401927414014</v>
       </c>
       <c r="T28">
-        <v>1.101040653557877</v>
+        <v>1.113768711514733</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.86904860969395</v>
+        <v>13.35538014266825</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08601114070122301</v>
+        <v>0.0858673539344128</v>
       </c>
       <c r="C29">
-        <v>833.2336615343115</v>
+        <v>825.5839056466614</v>
       </c>
       <c r="D29">
-        <v>851.3686615343116</v>
+        <v>854.4239056466615</v>
       </c>
       <c r="E29">
-        <v>-88.16499999999996</v>
+        <v>-77.45999999999998</v>
       </c>
       <c r="F29">
-        <v>289.035</v>
+        <v>299.74</v>
       </c>
       <c r="G29">
         <v>270.9</v>
@@ -3659,28 +3659,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M29">
-        <v>14.5384605</v>
+        <v>15.076922</v>
       </c>
       <c r="N29">
-        <v>179.6282061666667</v>
+        <v>179.0897446666667</v>
       </c>
       <c r="O29">
-        <v>35.92564123333334</v>
+        <v>35.81794893333334</v>
       </c>
       <c r="P29">
-        <v>143.7025649333333</v>
+        <v>143.2717957333334</v>
       </c>
       <c r="Q29">
-        <v>201.7025649333333</v>
+        <v>201.2717957333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1029401927414014</v>
+        <v>0.1036113249089067</v>
       </c>
       <c r="T29">
-        <v>1.113768711514733</v>
+        <v>1.126850326637058</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.35538014266825</v>
+        <v>12.8784022804301</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0858673539344128</v>
+        <v>0.0860715671676026</v>
       </c>
       <c r="C30">
-        <v>825.5839056466614</v>
+        <v>810.546204424467</v>
       </c>
       <c r="D30">
-        <v>854.4239056466615</v>
+        <v>850.091204424467</v>
       </c>
       <c r="E30">
-        <v>-77.45999999999998</v>
+        <v>-66.75499999999994</v>
       </c>
       <c r="F30">
-        <v>299.74</v>
+        <v>310.4450000000001</v>
       </c>
       <c r="G30">
         <v>270.9</v>
@@ -3741,45 +3741,45 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M30">
-        <v>15.076922</v>
+        <v>16.081051</v>
       </c>
       <c r="N30">
-        <v>179.0897446666667</v>
+        <v>178.0856156666667</v>
       </c>
       <c r="O30">
-        <v>35.81794893333334</v>
+        <v>35.61712313333334</v>
       </c>
       <c r="P30">
-        <v>143.2717957333334</v>
+        <v>142.4684925333333</v>
       </c>
       <c r="Q30">
-        <v>201.2717957333334</v>
+        <v>200.4684925333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1036113249089067</v>
+        <v>0.104301362207891</v>
       </c>
       <c r="T30">
-        <v>1.126850326637058</v>
+        <v>1.140300437960012</v>
       </c>
       <c r="U30">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>12.8784022804301</v>
+        <v>12.07425227783101</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0860715671676026</v>
+        <v>0.08593978040079241</v>
       </c>
       <c r="C31">
-        <v>810.5462044244671</v>
+        <v>802.6322204740385</v>
       </c>
       <c r="D31">
-        <v>850.091204424467</v>
+        <v>852.8822204740385</v>
       </c>
       <c r="E31">
-        <v>-66.755</v>
+        <v>-56.05000000000001</v>
       </c>
       <c r="F31">
-        <v>310.445</v>
+        <v>321.15</v>
       </c>
       <c r="G31">
         <v>270.9</v>
@@ -3823,28 +3823,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M31">
-        <v>16.081051</v>
+        <v>16.63557</v>
       </c>
       <c r="N31">
-        <v>178.0856156666667</v>
+        <v>177.5310966666667</v>
       </c>
       <c r="O31">
-        <v>35.61712313333334</v>
+        <v>35.50621933333334</v>
       </c>
       <c r="P31">
-        <v>142.4684925333333</v>
+        <v>142.0248773333333</v>
       </c>
       <c r="Q31">
-        <v>200.4684925333333</v>
+        <v>200.0248773333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.104301362207891</v>
+        <v>0.1050111148582749</v>
       </c>
       <c r="T31">
-        <v>1.140300437960012</v>
+        <v>1.154134838177907</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.07425227783101</v>
+        <v>11.67177720190331</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08593978040079241</v>
+        <v>0.08580799363398223</v>
       </c>
       <c r="C32">
-        <v>802.6322204740385</v>
+        <v>794.7366237981455</v>
       </c>
       <c r="D32">
-        <v>852.8822204740385</v>
+        <v>855.6916237981454</v>
       </c>
       <c r="E32">
-        <v>-56.05000000000001</v>
+        <v>-45.34499999999997</v>
       </c>
       <c r="F32">
-        <v>321.15</v>
+        <v>331.855</v>
       </c>
       <c r="G32">
         <v>270.9</v>
@@ -3905,28 +3905,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M32">
-        <v>16.63557</v>
+        <v>17.190089</v>
       </c>
       <c r="N32">
-        <v>177.5310966666667</v>
+        <v>176.9765776666667</v>
       </c>
       <c r="O32">
-        <v>35.50621933333334</v>
+        <v>35.39531553333334</v>
       </c>
       <c r="P32">
-        <v>142.0248773333333</v>
+        <v>141.5812621333334</v>
       </c>
       <c r="Q32">
-        <v>200.0248773333333</v>
+        <v>199.5812621333334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1050111148582749</v>
+        <v>0.1057414400492496</v>
       </c>
       <c r="T32">
-        <v>1.154134838177907</v>
+        <v>1.168370235503567</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.67177720190331</v>
+        <v>11.29526825990643</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08580799363398223</v>
+        <v>0.08567620686717202</v>
       </c>
       <c r="C33">
-        <v>794.7366237981455</v>
+        <v>786.8595967009487</v>
       </c>
       <c r="D33">
-        <v>855.6916237981454</v>
+        <v>858.5195967009486</v>
       </c>
       <c r="E33">
-        <v>-45.34499999999997</v>
+        <v>-34.63999999999999</v>
       </c>
       <c r="F33">
-        <v>331.855</v>
+        <v>342.56</v>
       </c>
       <c r="G33">
         <v>270.9</v>
@@ -3987,28 +3987,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M33">
-        <v>17.190089</v>
+        <v>17.744608</v>
       </c>
       <c r="N33">
-        <v>176.9765776666667</v>
+        <v>176.4220586666667</v>
       </c>
       <c r="O33">
-        <v>35.39531553333334</v>
+        <v>35.28441173333334</v>
       </c>
       <c r="P33">
-        <v>141.5812621333334</v>
+        <v>141.1376469333333</v>
       </c>
       <c r="Q33">
-        <v>199.5812621333334</v>
+        <v>199.1376469333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1057414400492496</v>
+        <v>0.1064932453929</v>
       </c>
       <c r="T33">
-        <v>1.168370235503567</v>
+        <v>1.183024320985864</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.29526825990643</v>
+        <v>10.94229112678436</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08567620686717202</v>
+        <v>0.08554442010036181</v>
       </c>
       <c r="C34">
-        <v>786.8595967009487</v>
+        <v>779.0013239045841</v>
       </c>
       <c r="D34">
-        <v>858.5195967009486</v>
+        <v>861.3663239045841</v>
       </c>
       <c r="E34">
-        <v>-34.63999999999999</v>
+        <v>-23.93499999999995</v>
       </c>
       <c r="F34">
-        <v>342.56</v>
+        <v>353.265</v>
       </c>
       <c r="G34">
         <v>270.9</v>
@@ -4069,28 +4069,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M34">
-        <v>17.744608</v>
+        <v>18.299127</v>
       </c>
       <c r="N34">
-        <v>176.4220586666667</v>
+        <v>175.8675396666667</v>
       </c>
       <c r="O34">
-        <v>35.28441173333334</v>
+        <v>35.17350793333334</v>
       </c>
       <c r="P34">
-        <v>141.1376469333333</v>
+        <v>140.6940317333334</v>
       </c>
       <c r="Q34">
-        <v>199.1376469333334</v>
+        <v>198.6940317333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1064932453929</v>
+        <v>0.1072674926871072</v>
       </c>
       <c r="T34">
-        <v>1.183024320985864</v>
+        <v>1.198115841855693</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.94229112678436</v>
+        <v>10.61070654718483</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08554442010036181</v>
+        <v>0.08541263333355163</v>
       </c>
       <c r="C35">
-        <v>779.0013239045841</v>
+        <v>771.1619925893876</v>
       </c>
       <c r="D35">
-        <v>861.3663239045841</v>
+        <v>864.2319925893876</v>
       </c>
       <c r="E35">
-        <v>-23.93499999999995</v>
+        <v>-13.22999999999996</v>
       </c>
       <c r="F35">
-        <v>353.265</v>
+        <v>363.97</v>
       </c>
       <c r="G35">
         <v>270.9</v>
@@ -4151,28 +4151,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M35">
-        <v>18.299127</v>
+        <v>18.853646</v>
       </c>
       <c r="N35">
-        <v>175.8675396666667</v>
+        <v>175.3130206666667</v>
       </c>
       <c r="O35">
-        <v>35.17350793333334</v>
+        <v>35.06260413333334</v>
       </c>
       <c r="P35">
-        <v>140.6940317333334</v>
+        <v>140.2504165333334</v>
       </c>
       <c r="Q35">
-        <v>198.6940317333334</v>
+        <v>198.2504165333334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1072674926871072</v>
+        <v>0.1080652020205328</v>
       </c>
       <c r="T35">
-        <v>1.198115841855693</v>
+        <v>1.213664681539759</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.61070654718483</v>
+        <v>10.29862694285586</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08541263333355163</v>
+        <v>0.08528084656674141</v>
       </c>
       <c r="C36">
-        <v>771.1619925893876</v>
+        <v>763.3417924349221</v>
       </c>
       <c r="D36">
-        <v>864.2319925893876</v>
+        <v>867.1167924349221</v>
       </c>
       <c r="E36">
-        <v>-13.22999999999996</v>
+        <v>-2.524999999999977</v>
       </c>
       <c r="F36">
-        <v>363.97</v>
+        <v>374.675</v>
       </c>
       <c r="G36">
         <v>270.9</v>
@@ -4233,28 +4233,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M36">
-        <v>18.853646</v>
+        <v>19.408165</v>
       </c>
       <c r="N36">
-        <v>175.3130206666667</v>
+        <v>174.7585016666667</v>
       </c>
       <c r="O36">
-        <v>35.06260413333334</v>
+        <v>34.95170033333334</v>
       </c>
       <c r="P36">
-        <v>140.2504165333334</v>
+        <v>139.8068013333333</v>
       </c>
       <c r="Q36">
-        <v>198.2504165333334</v>
+        <v>197.8068013333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1080652020205328</v>
+        <v>0.1088874562565253</v>
       </c>
       <c r="T36">
-        <v>1.213664681539759</v>
+        <v>1.229691947060258</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.29862694285586</v>
+        <v>10.00438045877427</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08528084656674141</v>
+        <v>0.08563865979993124</v>
       </c>
       <c r="C37">
-        <v>763.3417924349221</v>
+        <v>744.848732680591</v>
       </c>
       <c r="D37">
-        <v>867.1167924349221</v>
+        <v>859.3287326805911</v>
       </c>
       <c r="E37">
-        <v>-2.524999999999977</v>
+        <v>8.180000000000064</v>
       </c>
       <c r="F37">
-        <v>374.675</v>
+        <v>385.3800000000001</v>
       </c>
       <c r="G37">
         <v>270.9</v>
@@ -4315,45 +4315,45 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M37">
-        <v>19.408165</v>
+        <v>20.61783</v>
       </c>
       <c r="N37">
-        <v>174.7585016666667</v>
+        <v>173.5488366666667</v>
       </c>
       <c r="O37">
-        <v>34.95170033333334</v>
+        <v>34.70976733333334</v>
       </c>
       <c r="P37">
-        <v>139.8068013333333</v>
+        <v>138.8390693333334</v>
       </c>
       <c r="Q37">
-        <v>197.8068013333333</v>
+        <v>196.8390693333334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1088874562565253</v>
+        <v>0.1097354059373926</v>
       </c>
       <c r="T37">
-        <v>1.229691947060258</v>
+        <v>1.246220064628272</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>10.00438045877427</v>
+        <v>9.417415250133825</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08563865979993122</v>
+        <v>0.08552047303312105</v>
       </c>
       <c r="C38">
-        <v>744.8487326805913</v>
+        <v>736.7006328579359</v>
       </c>
       <c r="D38">
-        <v>859.3287326805912</v>
+        <v>861.885632857936</v>
       </c>
       <c r="E38">
-        <v>8.180000000000007</v>
+        <v>18.88499999999999</v>
       </c>
       <c r="F38">
-        <v>385.38</v>
+        <v>396.085</v>
       </c>
       <c r="G38">
         <v>270.9</v>
@@ -4397,28 +4397,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M38">
-        <v>20.61783</v>
+        <v>21.1905475</v>
       </c>
       <c r="N38">
-        <v>173.5488366666667</v>
+        <v>172.9761191666667</v>
       </c>
       <c r="O38">
-        <v>34.70976733333334</v>
+        <v>34.59522383333334</v>
       </c>
       <c r="P38">
-        <v>138.8390693333334</v>
+        <v>138.3808953333333</v>
       </c>
       <c r="Q38">
-        <v>196.8390693333334</v>
+        <v>196.3808953333333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1097354059373925</v>
+        <v>0.1106102746557477</v>
       </c>
       <c r="T38">
-        <v>1.246220064628272</v>
+        <v>1.263272884341302</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.417415250133827</v>
+        <v>9.162890513643722</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08552047303312105</v>
+        <v>0.08540228626631083</v>
       </c>
       <c r="C39">
-        <v>736.7006328579359</v>
+        <v>728.5677943645387</v>
       </c>
       <c r="D39">
-        <v>861.885632857936</v>
+        <v>864.4577943645386</v>
       </c>
       <c r="E39">
-        <v>18.88499999999999</v>
+        <v>29.59000000000003</v>
       </c>
       <c r="F39">
-        <v>396.085</v>
+        <v>406.79</v>
       </c>
       <c r="G39">
         <v>270.9</v>
@@ -4479,28 +4479,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M39">
-        <v>21.1905475</v>
+        <v>21.763265</v>
       </c>
       <c r="N39">
-        <v>172.9761191666667</v>
+        <v>172.4034016666667</v>
       </c>
       <c r="O39">
-        <v>34.59522383333334</v>
+        <v>34.48068033333334</v>
       </c>
       <c r="P39">
-        <v>138.3808953333333</v>
+        <v>137.9227213333334</v>
       </c>
       <c r="Q39">
-        <v>196.3808953333333</v>
+        <v>195.9227213333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1106102746557477</v>
+        <v>0.1115133649456626</v>
       </c>
       <c r="T39">
-        <v>1.263272884341302</v>
+        <v>1.280875795012818</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.162890513643722</v>
+        <v>8.921761815916256</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08540228626631083</v>
+        <v>0.08528409949950064</v>
       </c>
       <c r="C40">
-        <v>728.5677943645387</v>
+        <v>720.4503542444621</v>
       </c>
       <c r="D40">
-        <v>864.4577943645386</v>
+        <v>867.0453542444621</v>
       </c>
       <c r="E40">
-        <v>29.59000000000003</v>
+        <v>40.29500000000002</v>
       </c>
       <c r="F40">
-        <v>406.79</v>
+        <v>417.495</v>
       </c>
       <c r="G40">
         <v>270.9</v>
@@ -4561,28 +4561,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M40">
-        <v>21.763265</v>
+        <v>22.3359825</v>
       </c>
       <c r="N40">
-        <v>172.4034016666667</v>
+        <v>171.8306841666667</v>
       </c>
       <c r="O40">
-        <v>34.48068033333334</v>
+        <v>34.36613683333334</v>
       </c>
       <c r="P40">
-        <v>137.9227213333334</v>
+        <v>137.4645473333333</v>
       </c>
       <c r="Q40">
-        <v>195.9227213333334</v>
+        <v>195.4645473333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1115133649456626</v>
+        <v>0.1124460647532797</v>
       </c>
       <c r="T40">
-        <v>1.280875795012818</v>
+        <v>1.299055850296514</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.921761815916256</v>
+        <v>8.692998692431223</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08528409949950064</v>
+        <v>0.08516591273269045</v>
       </c>
       <c r="C41">
-        <v>720.4503542444621</v>
+        <v>712.3484511875401</v>
       </c>
       <c r="D41">
-        <v>867.0453542444621</v>
+        <v>869.6484511875402</v>
       </c>
       <c r="E41">
-        <v>40.29500000000002</v>
+        <v>51.00000000000006</v>
       </c>
       <c r="F41">
-        <v>417.495</v>
+        <v>428.2</v>
       </c>
       <c r="G41">
         <v>270.9</v>
@@ -4643,28 +4643,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M41">
-        <v>22.3359825</v>
+        <v>22.9087</v>
       </c>
       <c r="N41">
-        <v>171.8306841666667</v>
+        <v>171.2579666666667</v>
       </c>
       <c r="O41">
-        <v>34.36613683333334</v>
+        <v>34.25159333333334</v>
       </c>
       <c r="P41">
-        <v>137.4645473333333</v>
+        <v>137.0063733333333</v>
       </c>
       <c r="Q41">
-        <v>195.4645473333334</v>
+        <v>195.0063733333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1124460647532797</v>
+        <v>0.1134098545544841</v>
       </c>
       <c r="T41">
-        <v>1.299055850296514</v>
+        <v>1.317841907423</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.692998692431223</v>
+        <v>8.475673725120441</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08516591273269045</v>
+        <v>0.08504772596588026</v>
       </c>
       <c r="C42">
-        <v>712.3484511875401</v>
+        <v>704.2622255541544</v>
       </c>
       <c r="D42">
-        <v>869.6484511875402</v>
+        <v>872.2672255541545</v>
       </c>
       <c r="E42">
-        <v>51.00000000000006</v>
+        <v>61.70500000000004</v>
       </c>
       <c r="F42">
-        <v>428.2</v>
+        <v>438.905</v>
       </c>
       <c r="G42">
         <v>270.9</v>
@@ -4725,28 +4725,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M42">
-        <v>22.9087</v>
+        <v>23.4814175</v>
       </c>
       <c r="N42">
-        <v>171.2579666666667</v>
+        <v>170.6852491666667</v>
       </c>
       <c r="O42">
-        <v>34.25159333333334</v>
+        <v>34.13704983333334</v>
       </c>
       <c r="P42">
-        <v>137.0063733333333</v>
+        <v>136.5481993333333</v>
       </c>
       <c r="Q42">
-        <v>195.0063733333333</v>
+        <v>194.5481993333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1134098545544841</v>
+        <v>0.1144063151964072</v>
       </c>
       <c r="T42">
-        <v>1.317841907423</v>
+        <v>1.337264780045299</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.475673725120441</v>
+        <v>8.26894997572726</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08504772596588026</v>
+        <v>0.08492953919907005</v>
       </c>
       <c r="C43">
-        <v>704.2622255541544</v>
+        <v>696.1918194004627</v>
       </c>
       <c r="D43">
-        <v>872.2672255541545</v>
+        <v>874.9018194004628</v>
       </c>
       <c r="E43">
-        <v>61.70500000000004</v>
+        <v>72.41000000000008</v>
       </c>
       <c r="F43">
-        <v>438.905</v>
+        <v>449.6100000000001</v>
       </c>
       <c r="G43">
         <v>270.9</v>
@@ -4807,28 +4807,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M43">
-        <v>23.4814175</v>
+        <v>24.054135</v>
       </c>
       <c r="N43">
-        <v>170.6852491666667</v>
+        <v>170.1125316666667</v>
       </c>
       <c r="O43">
-        <v>34.13704983333334</v>
+        <v>34.02250633333334</v>
       </c>
       <c r="P43">
-        <v>136.5481993333333</v>
+        <v>136.0900253333334</v>
       </c>
       <c r="Q43">
-        <v>194.5481993333333</v>
+        <v>194.0900253333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1144063151964072</v>
+        <v>0.1154371365501208</v>
       </c>
       <c r="T43">
-        <v>1.337264780045299</v>
+        <v>1.357357406895954</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.26894997572726</v>
+        <v>8.072070214400421</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08492953919907006</v>
+        <v>0.08481135243225986</v>
       </c>
       <c r="C44">
-        <v>696.1918194004627</v>
+        <v>688.1373765040867</v>
       </c>
       <c r="D44">
-        <v>874.9018194004625</v>
+        <v>877.5523765040866</v>
       </c>
       <c r="E44">
-        <v>72.40999999999997</v>
+        <v>83.11500000000001</v>
       </c>
       <c r="F44">
-        <v>449.61</v>
+        <v>460.315</v>
       </c>
       <c r="G44">
         <v>270.9</v>
@@ -4889,28 +4889,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M44">
-        <v>24.054135</v>
+        <v>24.6268525</v>
       </c>
       <c r="N44">
-        <v>170.1125316666667</v>
+        <v>169.5398141666667</v>
       </c>
       <c r="O44">
-        <v>34.02250633333334</v>
+        <v>33.90796283333334</v>
       </c>
       <c r="P44">
-        <v>136.0900253333334</v>
+        <v>135.6318513333334</v>
       </c>
       <c r="Q44">
-        <v>194.0900253333334</v>
+        <v>193.6318513333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1154371365501208</v>
+        <v>0.1165041270741401</v>
       </c>
       <c r="T44">
-        <v>1.357357406895954</v>
+        <v>1.378155038197508</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.072070214400423</v>
+        <v>7.884347651274831</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08481135243225986</v>
+        <v>0.08469316566544967</v>
       </c>
       <c r="C45">
-        <v>688.1373765040867</v>
+        <v>680.099042390267</v>
       </c>
       <c r="D45">
-        <v>877.5523765040866</v>
+        <v>880.219042390267</v>
       </c>
       <c r="E45">
-        <v>83.11500000000001</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="F45">
-        <v>460.315</v>
+        <v>471.02</v>
       </c>
       <c r="G45">
         <v>270.9</v>
@@ -4971,28 +4971,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M45">
-        <v>24.6268525</v>
+        <v>25.19957</v>
       </c>
       <c r="N45">
-        <v>169.5398141666667</v>
+        <v>168.9670966666667</v>
       </c>
       <c r="O45">
-        <v>33.90796283333334</v>
+        <v>33.79341933333334</v>
       </c>
       <c r="P45">
-        <v>135.6318513333334</v>
+        <v>135.1736773333334</v>
       </c>
       <c r="Q45">
-        <v>193.6318513333334</v>
+        <v>193.1736773333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1165041270741401</v>
+        <v>0.1176092244025887</v>
       </c>
       <c r="T45">
-        <v>1.378155038197508</v>
+        <v>1.399695442045547</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.884347651274831</v>
+        <v>7.705157931927676</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08469316566544967</v>
+        <v>0.08486297889863947</v>
       </c>
       <c r="C46">
-        <v>680.099042390267</v>
+        <v>665.5675845594041</v>
       </c>
       <c r="D46">
-        <v>880.219042390267</v>
+        <v>876.3925845594041</v>
       </c>
       <c r="E46">
-        <v>93.81999999999999</v>
+        <v>104.525</v>
       </c>
       <c r="F46">
-        <v>471.02</v>
+        <v>481.725</v>
       </c>
       <c r="G46">
         <v>270.9</v>
@@ -5053,45 +5053,45 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M46">
-        <v>25.19957</v>
+        <v>26.1576675</v>
       </c>
       <c r="N46">
-        <v>168.9670966666667</v>
+        <v>168.0089991666667</v>
       </c>
       <c r="O46">
-        <v>33.79341933333334</v>
+        <v>33.60179983333334</v>
       </c>
       <c r="P46">
-        <v>135.1736773333334</v>
+        <v>134.4071993333334</v>
       </c>
       <c r="Q46">
-        <v>193.1736773333334</v>
+        <v>192.4071993333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1176092244025887</v>
+        <v>0.1187545070884354</v>
       </c>
       <c r="T46">
-        <v>1.399695442045547</v>
+        <v>1.422019133306241</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.705157931927676</v>
+        <v>7.422935040621136</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08486297889863947</v>
+        <v>0.08475119213182927</v>
       </c>
       <c r="C47">
-        <v>665.5675845594041</v>
+        <v>657.3777602991545</v>
       </c>
       <c r="D47">
-        <v>876.3925845594041</v>
+        <v>878.9077602991546</v>
       </c>
       <c r="E47">
-        <v>104.525</v>
+        <v>115.23</v>
       </c>
       <c r="F47">
-        <v>481.725</v>
+        <v>492.43</v>
       </c>
       <c r="G47">
         <v>270.9</v>
@@ -5135,28 +5135,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M47">
-        <v>26.1576675</v>
+        <v>26.738949</v>
       </c>
       <c r="N47">
-        <v>168.0089991666667</v>
+        <v>167.4277176666667</v>
       </c>
       <c r="O47">
-        <v>33.60179983333334</v>
+        <v>33.48554353333334</v>
       </c>
       <c r="P47">
-        <v>134.4071993333334</v>
+        <v>133.9421741333334</v>
       </c>
       <c r="Q47">
-        <v>192.4071993333334</v>
+        <v>191.9421741333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1187545070884354</v>
+        <v>0.1199422076515357</v>
       </c>
       <c r="T47">
-        <v>1.422019133306241</v>
+        <v>1.445169627946961</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.422935040621136</v>
+        <v>7.261566887564156</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08475119213182927</v>
+        <v>0.0846394053650191</v>
       </c>
       <c r="C48">
-        <v>657.3777602991545</v>
+        <v>649.2024142916614</v>
       </c>
       <c r="D48">
-        <v>878.9077602991546</v>
+        <v>881.4374142916614</v>
       </c>
       <c r="E48">
-        <v>115.23</v>
+        <v>125.9350000000001</v>
       </c>
       <c r="F48">
-        <v>492.43</v>
+        <v>503.135</v>
       </c>
       <c r="G48">
         <v>270.9</v>
@@ -5217,28 +5217,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M48">
-        <v>26.738949</v>
+        <v>27.3202305</v>
       </c>
       <c r="N48">
-        <v>167.4277176666667</v>
+        <v>166.8464361666667</v>
       </c>
       <c r="O48">
-        <v>33.48554353333334</v>
+        <v>33.36928723333334</v>
       </c>
       <c r="P48">
-        <v>133.9421741333334</v>
+        <v>133.4771489333334</v>
       </c>
       <c r="Q48">
-        <v>191.9421741333334</v>
+        <v>191.4771489333334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1199422076515357</v>
+        <v>0.1211747271038096</v>
       </c>
       <c r="T48">
-        <v>1.445169627946961</v>
+        <v>1.46919372615903</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.261566887564156</v>
+        <v>7.107065464424491</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0846394053650191</v>
+        <v>0.08452761859820888</v>
       </c>
       <c r="C49">
-        <v>649.2024142916614</v>
+        <v>641.0416719107903</v>
       </c>
       <c r="D49">
-        <v>881.4374142916614</v>
+        <v>883.9816719107905</v>
       </c>
       <c r="E49">
-        <v>125.9350000000001</v>
+        <v>136.64</v>
       </c>
       <c r="F49">
-        <v>503.135</v>
+        <v>513.84</v>
       </c>
       <c r="G49">
         <v>270.9</v>
@@ -5299,28 +5299,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M49">
-        <v>27.3202305</v>
+        <v>27.901512</v>
       </c>
       <c r="N49">
-        <v>166.8464361666667</v>
+        <v>166.2651546666667</v>
       </c>
       <c r="O49">
-        <v>33.36928723333334</v>
+        <v>33.25303093333334</v>
       </c>
       <c r="P49">
-        <v>133.4771489333334</v>
+        <v>133.0121237333333</v>
       </c>
       <c r="Q49">
-        <v>191.4771489333334</v>
+        <v>191.0121237333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1211747271038096</v>
+        <v>0.1224546511504017</v>
       </c>
       <c r="T49">
-        <v>1.46919372615903</v>
+        <v>1.494141828148485</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.107065464424491</v>
+        <v>6.959001600582315</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08452761859820888</v>
+        <v>0.08441583183139868</v>
       </c>
       <c r="C50">
-        <v>641.0416719107903</v>
+        <v>632.8956599821555</v>
       </c>
       <c r="D50">
-        <v>883.9816719107905</v>
+        <v>886.5406599821555</v>
       </c>
       <c r="E50">
-        <v>136.64</v>
+        <v>147.345</v>
       </c>
       <c r="F50">
-        <v>513.84</v>
+        <v>524.545</v>
       </c>
       <c r="G50">
         <v>270.9</v>
@@ -5381,28 +5381,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M50">
-        <v>27.901512</v>
+        <v>28.4827935</v>
       </c>
       <c r="N50">
-        <v>166.2651546666667</v>
+        <v>165.6838731666667</v>
       </c>
       <c r="O50">
-        <v>33.25303093333334</v>
+        <v>33.13677463333334</v>
       </c>
       <c r="P50">
-        <v>133.0121237333333</v>
+        <v>132.5470985333333</v>
       </c>
       <c r="Q50">
-        <v>191.0121237333333</v>
+        <v>190.5470985333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1224546511504017</v>
+        <v>0.1237847682968602</v>
       </c>
       <c r="T50">
-        <v>1.494141828148485</v>
+        <v>1.520068287078703</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.959001600582315</v>
+        <v>6.816981159754104</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08441583183139868</v>
+        <v>0.08430404506458848</v>
       </c>
       <c r="C51">
-        <v>632.8956599821555</v>
+        <v>624.7645068041957</v>
       </c>
       <c r="D51">
-        <v>886.5406599821555</v>
+        <v>889.1145068041957</v>
       </c>
       <c r="E51">
-        <v>147.345</v>
+        <v>158.05</v>
       </c>
       <c r="F51">
-        <v>524.545</v>
+        <v>535.25</v>
       </c>
       <c r="G51">
         <v>270.9</v>
@@ -5463,28 +5463,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M51">
-        <v>28.4827935</v>
+        <v>29.064075</v>
       </c>
       <c r="N51">
-        <v>165.6838731666667</v>
+        <v>165.1025916666667</v>
       </c>
       <c r="O51">
-        <v>33.13677463333334</v>
+        <v>33.02051833333334</v>
       </c>
       <c r="P51">
-        <v>132.5470985333333</v>
+        <v>132.0820733333333</v>
       </c>
       <c r="Q51">
-        <v>190.5470985333333</v>
+        <v>190.0820733333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1237847682968602</v>
+        <v>0.125168090129177</v>
       </c>
       <c r="T51">
-        <v>1.520068287078703</v>
+        <v>1.547031804366131</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.816981159754104</v>
+        <v>6.680641536559023</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08430404506458848</v>
+        <v>0.08419225829777829</v>
       </c>
       <c r="C52">
-        <v>624.7645068041957</v>
+        <v>616.648342169617</v>
       </c>
       <c r="D52">
-        <v>889.1145068041957</v>
+        <v>891.703342169617</v>
       </c>
       <c r="E52">
-        <v>158.05</v>
+        <v>168.7550000000001</v>
       </c>
       <c r="F52">
-        <v>535.25</v>
+        <v>545.955</v>
       </c>
       <c r="G52">
         <v>270.9</v>
@@ -5545,28 +5545,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M52">
-        <v>29.064075</v>
+        <v>29.6453565</v>
       </c>
       <c r="N52">
-        <v>165.1025916666667</v>
+        <v>164.5213101666667</v>
       </c>
       <c r="O52">
-        <v>33.02051833333334</v>
+        <v>32.90426203333334</v>
       </c>
       <c r="P52">
-        <v>132.0820733333333</v>
+        <v>131.6170481333334</v>
       </c>
       <c r="Q52">
-        <v>190.0820733333334</v>
+        <v>189.6170481333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.125168090129177</v>
+        <v>0.1266078740770986</v>
       </c>
       <c r="T52">
-        <v>1.547031804366131</v>
+        <v>1.575095873379575</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.680641536559023</v>
+        <v>6.549648565253944</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08419225829777829</v>
+        <v>0.08408047153096809</v>
       </c>
       <c r="C53">
-        <v>616.648342169617</v>
+        <v>608.5472973872103</v>
       </c>
       <c r="D53">
-        <v>891.703342169617</v>
+        <v>894.3072973872103</v>
       </c>
       <c r="E53">
-        <v>168.7550000000001</v>
+        <v>179.46</v>
       </c>
       <c r="F53">
-        <v>545.955</v>
+        <v>556.66</v>
       </c>
       <c r="G53">
         <v>270.9</v>
@@ -5627,28 +5627,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M53">
-        <v>29.6453565</v>
+        <v>30.226638</v>
       </c>
       <c r="N53">
-        <v>164.5213101666667</v>
+        <v>163.9400286666667</v>
       </c>
       <c r="O53">
-        <v>32.90426203333334</v>
+        <v>32.78800573333334</v>
       </c>
       <c r="P53">
-        <v>131.6170481333334</v>
+        <v>131.1520229333333</v>
       </c>
       <c r="Q53">
-        <v>189.6170481333334</v>
+        <v>189.1520229333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1266078740770986</v>
+        <v>0.1281076490228502</v>
       </c>
       <c r="T53">
-        <v>1.575095873379575</v>
+        <v>1.604329278601913</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.549648565253944</v>
+        <v>6.423693785152907</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08408047153096809</v>
+        <v>0.08396868476415789</v>
       </c>
       <c r="C54">
-        <v>608.5472973872103</v>
+        <v>600.4615053040511</v>
       </c>
       <c r="D54">
-        <v>894.3072973872103</v>
+        <v>896.9265053040511</v>
       </c>
       <c r="E54">
-        <v>179.46</v>
+        <v>190.165</v>
       </c>
       <c r="F54">
-        <v>556.66</v>
+        <v>567.365</v>
       </c>
       <c r="G54">
         <v>270.9</v>
@@ -5709,28 +5709,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M54">
-        <v>30.226638</v>
+        <v>30.8079195</v>
       </c>
       <c r="N54">
-        <v>163.9400286666667</v>
+        <v>163.3587471666667</v>
       </c>
       <c r="O54">
-        <v>32.78800573333334</v>
+        <v>32.67174943333334</v>
       </c>
       <c r="P54">
-        <v>131.1520229333333</v>
+        <v>130.6869977333334</v>
       </c>
       <c r="Q54">
-        <v>189.1520229333333</v>
+        <v>188.6869977333334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1281076490228502</v>
+        <v>0.1296712441790593</v>
       </c>
       <c r="T54">
-        <v>1.604329278601913</v>
+        <v>1.634806658514564</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.423693785152907</v>
+        <v>6.30249201562172</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08396868476415789</v>
+        <v>0.08385689799734769</v>
       </c>
       <c r="C55">
-        <v>600.4615053040511</v>
+        <v>592.3911003280938</v>
       </c>
       <c r="D55">
-        <v>896.9265053040511</v>
+        <v>899.5611003280939</v>
       </c>
       <c r="E55">
-        <v>190.165</v>
+        <v>200.8700000000001</v>
       </c>
       <c r="F55">
-        <v>567.365</v>
+        <v>578.0700000000001</v>
       </c>
       <c r="G55">
         <v>270.9</v>
@@ -5791,28 +5791,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M55">
-        <v>30.8079195</v>
+        <v>31.389201</v>
       </c>
       <c r="N55">
-        <v>163.3587471666667</v>
+        <v>162.7774656666667</v>
       </c>
       <c r="O55">
-        <v>32.67174943333334</v>
+        <v>32.55549313333334</v>
       </c>
       <c r="P55">
-        <v>130.6869977333334</v>
+        <v>130.2219725333333</v>
       </c>
       <c r="Q55">
-        <v>188.6869977333334</v>
+        <v>188.2219725333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1296712441790593</v>
+        <v>0.1313028217333645</v>
       </c>
       <c r="T55">
-        <v>1.634806658514564</v>
+        <v>1.666609141901677</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.30249201562172</v>
+        <v>6.185779200517612</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08385689799734769</v>
+        <v>0.0841851112305375</v>
       </c>
       <c r="C56">
-        <v>592.3911003280938</v>
+        <v>573.9943717456954</v>
       </c>
       <c r="D56">
-        <v>899.5611003280939</v>
+        <v>891.8693717456954</v>
       </c>
       <c r="E56">
-        <v>200.8700000000001</v>
+        <v>211.5750000000001</v>
       </c>
       <c r="F56">
-        <v>578.0700000000001</v>
+        <v>588.7750000000001</v>
       </c>
       <c r="G56">
         <v>270.9</v>
@@ -5873,45 +5873,45 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M56">
-        <v>31.389201</v>
+        <v>32.55925750000001</v>
       </c>
       <c r="N56">
-        <v>162.7774656666667</v>
+        <v>161.6074091666667</v>
       </c>
       <c r="O56">
-        <v>32.55549313333334</v>
+        <v>32.32148183333334</v>
       </c>
       <c r="P56">
-        <v>130.2219725333333</v>
+        <v>129.2859273333333</v>
       </c>
       <c r="Q56">
-        <v>188.2219725333334</v>
+        <v>187.2859273333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1313028217333645</v>
+        <v>0.1330069138456389</v>
       </c>
       <c r="T56">
-        <v>1.666609141901677</v>
+        <v>1.699825068994884</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.185779200517612</v>
+        <v>5.96348570500008</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0841851112305375</v>
+        <v>0.08408132446372729</v>
       </c>
       <c r="C57">
-        <v>573.9943717456954</v>
+        <v>565.7073716400887</v>
       </c>
       <c r="D57">
-        <v>891.8693717456954</v>
+        <v>894.2873716400888</v>
       </c>
       <c r="E57">
-        <v>211.5750000000001</v>
+        <v>222.28</v>
       </c>
       <c r="F57">
-        <v>588.7750000000001</v>
+        <v>599.48</v>
       </c>
       <c r="G57">
         <v>270.9</v>
@@ -5955,28 +5955,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M57">
-        <v>32.55925750000001</v>
+        <v>33.15124400000001</v>
       </c>
       <c r="N57">
-        <v>161.6074091666667</v>
+        <v>161.0154226666667</v>
       </c>
       <c r="O57">
-        <v>32.32148183333334</v>
+        <v>32.20308453333333</v>
       </c>
       <c r="P57">
-        <v>129.2859273333333</v>
+        <v>128.8123381333333</v>
       </c>
       <c r="Q57">
-        <v>187.2859273333333</v>
+        <v>186.8123381333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1330069138456389</v>
+        <v>0.1347884646902893</v>
       </c>
       <c r="T57">
-        <v>1.699825068994884</v>
+        <v>1.734550810955965</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.96348570500008</v>
+        <v>5.856994888839364</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08408132446372729</v>
+        <v>0.0839775376969171</v>
       </c>
       <c r="C58">
-        <v>565.7073716400887</v>
+        <v>557.4335183431202</v>
       </c>
       <c r="D58">
-        <v>894.2873716400888</v>
+        <v>896.7185183431202</v>
       </c>
       <c r="E58">
-        <v>222.28</v>
+        <v>232.9850000000001</v>
       </c>
       <c r="F58">
-        <v>599.48</v>
+        <v>610.1850000000001</v>
       </c>
       <c r="G58">
         <v>270.9</v>
@@ -6037,28 +6037,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M58">
-        <v>33.15124400000001</v>
+        <v>33.7432305</v>
       </c>
       <c r="N58">
-        <v>161.0154226666667</v>
+        <v>160.4234361666667</v>
       </c>
       <c r="O58">
-        <v>32.20308453333333</v>
+        <v>32.08468723333333</v>
       </c>
       <c r="P58">
-        <v>128.8123381333333</v>
+        <v>128.3387489333333</v>
       </c>
       <c r="Q58">
-        <v>186.8123381333334</v>
+        <v>186.3387489333334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1347884646902893</v>
+        <v>0.1366528783649235</v>
       </c>
       <c r="T58">
-        <v>1.734550810955965</v>
+        <v>1.770891703705933</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.856994888839364</v>
+        <v>5.754240592543938</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0839775376969171</v>
+        <v>0.08387375093010691</v>
       </c>
       <c r="C59">
-        <v>557.4335183431202</v>
+        <v>549.1729193670305</v>
       </c>
       <c r="D59">
-        <v>896.7185183431202</v>
+        <v>899.1629193670306</v>
       </c>
       <c r="E59">
-        <v>232.9850000000001</v>
+        <v>243.6900000000001</v>
       </c>
       <c r="F59">
-        <v>610.1850000000001</v>
+        <v>620.8900000000001</v>
       </c>
       <c r="G59">
         <v>270.9</v>
@@ -6119,28 +6119,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M59">
-        <v>33.7432305</v>
+        <v>34.33521700000001</v>
       </c>
       <c r="N59">
-        <v>160.4234361666667</v>
+        <v>159.8314496666667</v>
       </c>
       <c r="O59">
-        <v>32.08468723333333</v>
+        <v>31.96628993333334</v>
       </c>
       <c r="P59">
-        <v>128.3387489333333</v>
+        <v>127.8651597333333</v>
       </c>
       <c r="Q59">
-        <v>186.3387489333334</v>
+        <v>185.8651597333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1366528783649235</v>
+        <v>0.1386060736431117</v>
       </c>
       <c r="T59">
-        <v>1.770891703705933</v>
+        <v>1.80896311515828</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.754240592543938</v>
+        <v>5.655029547844904</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08387375093010691</v>
+        <v>0.08376996416329673</v>
       </c>
       <c r="C60">
-        <v>549.1729193670307</v>
+        <v>540.9256833995527</v>
       </c>
       <c r="D60">
-        <v>899.1629193670306</v>
+        <v>901.6206833995527</v>
       </c>
       <c r="E60">
-        <v>243.69</v>
+        <v>254.3949999999999</v>
       </c>
       <c r="F60">
-        <v>620.89</v>
+        <v>631.5949999999999</v>
       </c>
       <c r="G60">
         <v>270.9</v>
@@ -6201,28 +6201,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M60">
-        <v>34.335217</v>
+        <v>34.9272035</v>
       </c>
       <c r="N60">
-        <v>159.8314496666667</v>
+        <v>159.2394631666667</v>
       </c>
       <c r="O60">
-        <v>31.96628993333334</v>
+        <v>31.84789263333334</v>
       </c>
       <c r="P60">
-        <v>127.8651597333333</v>
+        <v>127.3915705333334</v>
       </c>
       <c r="Q60">
-        <v>185.8651597333334</v>
+        <v>185.3915705333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1386060736431117</v>
+        <v>0.1406545467397481</v>
       </c>
       <c r="T60">
-        <v>1.808963115158279</v>
+        <v>1.848891668632693</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.655029547844904</v>
+        <v>5.559181589406856</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08376996416329673</v>
+        <v>0.08366617739648652</v>
       </c>
       <c r="C61">
-        <v>540.9256833995527</v>
+        <v>532.6919203200225</v>
       </c>
       <c r="D61">
-        <v>901.6206833995527</v>
+        <v>904.0919203200224</v>
       </c>
       <c r="E61">
-        <v>254.3949999999999</v>
+        <v>265.1</v>
       </c>
       <c r="F61">
-        <v>631.5949999999999</v>
+        <v>642.3</v>
       </c>
       <c r="G61">
         <v>270.9</v>
@@ -6283,28 +6283,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M61">
-        <v>34.9272035</v>
+        <v>35.51919</v>
       </c>
       <c r="N61">
-        <v>159.2394631666667</v>
+        <v>158.6474766666667</v>
       </c>
       <c r="O61">
-        <v>31.84789263333334</v>
+        <v>31.72949533333334</v>
       </c>
       <c r="P61">
-        <v>127.3915705333334</v>
+        <v>126.9179813333333</v>
       </c>
       <c r="Q61">
-        <v>185.3915705333334</v>
+        <v>184.9179813333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1406545467397481</v>
+        <v>0.1428054434912163</v>
       </c>
       <c r="T61">
-        <v>1.848891668632693</v>
+        <v>1.890816649780826</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.559181589406856</v>
+        <v>5.466528562916741</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08366617739648652</v>
+        <v>0.08356239062967633</v>
       </c>
       <c r="C62">
-        <v>532.6919203200225</v>
+        <v>524.4717412157494</v>
       </c>
       <c r="D62">
-        <v>904.0919203200224</v>
+        <v>906.5767412157494</v>
       </c>
       <c r="E62">
-        <v>265.1</v>
+        <v>275.805</v>
       </c>
       <c r="F62">
-        <v>642.3</v>
+        <v>653.005</v>
       </c>
       <c r="G62">
         <v>270.9</v>
@@ -6365,28 +6365,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M62">
-        <v>35.51919</v>
+        <v>36.1111765</v>
       </c>
       <c r="N62">
-        <v>158.6474766666667</v>
+        <v>158.0554901666667</v>
       </c>
       <c r="O62">
-        <v>31.72949533333334</v>
+        <v>31.61109803333334</v>
       </c>
       <c r="P62">
-        <v>126.9179813333333</v>
+        <v>126.4443921333334</v>
       </c>
       <c r="Q62">
-        <v>184.9179813333334</v>
+        <v>184.4443921333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1428054434912163</v>
+        <v>0.1450666426401957</v>
       </c>
       <c r="T62">
-        <v>1.890816649780826</v>
+        <v>1.934891629962197</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.466528562916741</v>
+        <v>5.376913340573844</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08356239062967633</v>
+        <v>0.08345860386286612</v>
       </c>
       <c r="C63">
-        <v>524.4717412157494</v>
+        <v>516.2652583986687</v>
       </c>
       <c r="D63">
-        <v>906.5767412157494</v>
+        <v>909.0752583986688</v>
       </c>
       <c r="E63">
-        <v>275.805</v>
+        <v>286.51</v>
       </c>
       <c r="F63">
-        <v>653.005</v>
+        <v>663.71</v>
       </c>
       <c r="G63">
         <v>270.9</v>
@@ -6447,28 +6447,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M63">
-        <v>36.1111765</v>
+        <v>36.703163</v>
       </c>
       <c r="N63">
-        <v>158.0554901666667</v>
+        <v>157.4635036666667</v>
       </c>
       <c r="O63">
-        <v>31.61109803333334</v>
+        <v>31.49270073333334</v>
       </c>
       <c r="P63">
-        <v>126.4443921333334</v>
+        <v>125.9708029333333</v>
       </c>
       <c r="Q63">
-        <v>184.4443921333334</v>
+        <v>183.9708029333333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1450666426401957</v>
+        <v>0.1474468522707003</v>
       </c>
       <c r="T63">
-        <v>1.934891629962197</v>
+        <v>1.981286345942588</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.376913340573844</v>
+        <v>5.29018893185491</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08345860386286612</v>
+        <v>0.08335481709605592</v>
       </c>
       <c r="C64">
-        <v>516.2652583986687</v>
+        <v>508.0725854222569</v>
       </c>
       <c r="D64">
-        <v>909.0752583986688</v>
+        <v>911.5875854222569</v>
       </c>
       <c r="E64">
-        <v>286.51</v>
+        <v>297.215</v>
       </c>
       <c r="F64">
-        <v>663.71</v>
+        <v>674.415</v>
       </c>
       <c r="G64">
         <v>270.9</v>
@@ -6529,28 +6529,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M64">
-        <v>36.703163</v>
+        <v>37.2951495</v>
       </c>
       <c r="N64">
-        <v>157.4635036666667</v>
+        <v>156.8715171666667</v>
       </c>
       <c r="O64">
-        <v>31.49270073333334</v>
+        <v>31.37430343333334</v>
       </c>
       <c r="P64">
-        <v>125.9708029333333</v>
+        <v>125.4972137333333</v>
       </c>
       <c r="Q64">
-        <v>183.9708029333333</v>
+        <v>183.4972137333334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1474468522707003</v>
+        <v>0.1499557218812322</v>
       </c>
       <c r="T64">
-        <v>1.981286345942588</v>
+        <v>2.030188884408406</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.29018893185491</v>
+        <v>5.206217678968325</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08335481709605592</v>
+        <v>0.08325103032924573</v>
       </c>
       <c r="C65">
-        <v>508.0725854222569</v>
+        <v>499.8938370987402</v>
       </c>
       <c r="D65">
-        <v>911.5875854222569</v>
+        <v>914.1138370987403</v>
       </c>
       <c r="E65">
-        <v>297.215</v>
+        <v>307.92</v>
       </c>
       <c r="F65">
-        <v>674.415</v>
+        <v>685.12</v>
       </c>
       <c r="G65">
         <v>270.9</v>
@@ -6611,28 +6611,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M65">
-        <v>37.2951495</v>
+        <v>37.887136</v>
       </c>
       <c r="N65">
-        <v>156.8715171666667</v>
+        <v>156.2795306666667</v>
       </c>
       <c r="O65">
-        <v>31.37430343333334</v>
+        <v>31.25590613333334</v>
       </c>
       <c r="P65">
-        <v>125.4972137333333</v>
+        <v>125.0236245333333</v>
       </c>
       <c r="Q65">
-        <v>183.4972137333334</v>
+        <v>183.0236245333334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1499557218812322</v>
+        <v>0.1526039731367937</v>
       </c>
       <c r="T65">
-        <v>2.030188884408406</v>
+        <v>2.081808230566768</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.206217678968325</v>
+        <v>5.124870527734445</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08325103032924573</v>
+        <v>0.08314724356243554</v>
       </c>
       <c r="C66">
-        <v>499.8938370987402</v>
+        <v>491.7291295165817</v>
       </c>
       <c r="D66">
-        <v>914.1138370987403</v>
+        <v>916.6541295165819</v>
       </c>
       <c r="E66">
-        <v>307.92</v>
+        <v>318.6250000000001</v>
       </c>
       <c r="F66">
-        <v>685.12</v>
+        <v>695.825</v>
       </c>
       <c r="G66">
         <v>270.9</v>
@@ -6693,28 +6693,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M66">
-        <v>37.887136</v>
+        <v>38.4791225</v>
       </c>
       <c r="N66">
-        <v>156.2795306666667</v>
+        <v>155.6875441666667</v>
       </c>
       <c r="O66">
-        <v>31.25590613333334</v>
+        <v>31.13750883333334</v>
       </c>
       <c r="P66">
-        <v>125.0236245333333</v>
+        <v>124.5500353333333</v>
       </c>
       <c r="Q66">
-        <v>183.0236245333334</v>
+        <v>182.5500353333334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1526039731367937</v>
+        <v>0.1554035530355301</v>
       </c>
       <c r="T66">
-        <v>2.081808230566768</v>
+        <v>2.136377253648466</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.124870527734445</v>
+        <v>5.046026365769299</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08314724356243554</v>
+        <v>0.08304345679562533</v>
       </c>
       <c r="C67">
-        <v>491.7291295165817</v>
+        <v>483.5785800582654</v>
       </c>
       <c r="D67">
-        <v>916.6541295165819</v>
+        <v>919.2085800582654</v>
       </c>
       <c r="E67">
-        <v>318.6250000000001</v>
+        <v>329.3300000000001</v>
       </c>
       <c r="F67">
-        <v>695.825</v>
+        <v>706.5300000000001</v>
       </c>
       <c r="G67">
         <v>270.9</v>
@@ -6775,28 +6775,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M67">
-        <v>38.4791225</v>
+        <v>39.07110900000001</v>
       </c>
       <c r="N67">
-        <v>155.6875441666667</v>
+        <v>155.0955576666667</v>
       </c>
       <c r="O67">
-        <v>31.13750883333334</v>
+        <v>31.01911153333334</v>
       </c>
       <c r="P67">
-        <v>124.5500353333333</v>
+        <v>124.0764461333333</v>
       </c>
       <c r="Q67">
-        <v>182.5500353333334</v>
+        <v>182.0764461333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1554035530355301</v>
+        <v>0.1583678141047804</v>
       </c>
       <c r="T67">
-        <v>2.136377253648466</v>
+        <v>2.194156219264381</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.046026365769299</v>
+        <v>4.9695714208334</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08304345679562533</v>
+        <v>0.08293967002881514</v>
       </c>
       <c r="C68">
-        <v>483.5785800582654</v>
+        <v>475.4423074183743</v>
       </c>
       <c r="D68">
-        <v>919.2085800582654</v>
+        <v>921.7773074183744</v>
       </c>
       <c r="E68">
-        <v>329.3300000000001</v>
+        <v>340.035</v>
       </c>
       <c r="F68">
-        <v>706.5300000000001</v>
+        <v>717.235</v>
       </c>
       <c r="G68">
         <v>270.9</v>
@@ -6857,28 +6857,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M68">
-        <v>39.07110900000001</v>
+        <v>39.6630955</v>
       </c>
       <c r="N68">
-        <v>155.0955576666667</v>
+        <v>154.5035711666667</v>
       </c>
       <c r="O68">
-        <v>31.01911153333334</v>
+        <v>30.90071423333334</v>
       </c>
       <c r="P68">
-        <v>124.0764461333333</v>
+        <v>123.6028569333334</v>
       </c>
       <c r="Q68">
-        <v>182.0764461333334</v>
+        <v>181.6028569333334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1583678141047804</v>
+        <v>0.1615117273600459</v>
       </c>
       <c r="T68">
-        <v>2.194156219264381</v>
+        <v>2.255436940372171</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.9695714208334</v>
+        <v>4.895398713059768</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08293967002881514</v>
+        <v>0.08283588326200494</v>
       </c>
       <c r="C69">
-        <v>475.4423074183743</v>
+        <v>467.320431621979</v>
       </c>
       <c r="D69">
-        <v>921.7773074183744</v>
+        <v>924.360431621979</v>
       </c>
       <c r="E69">
-        <v>340.035</v>
+        <v>350.7400000000001</v>
       </c>
       <c r="F69">
-        <v>717.235</v>
+        <v>727.9400000000001</v>
       </c>
       <c r="G69">
         <v>270.9</v>
@@ -6939,28 +6939,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M69">
-        <v>39.6630955</v>
+        <v>40.255082</v>
       </c>
       <c r="N69">
-        <v>154.5035711666667</v>
+        <v>153.9115846666667</v>
       </c>
       <c r="O69">
-        <v>30.90071423333334</v>
+        <v>30.78231693333333</v>
       </c>
       <c r="P69">
-        <v>123.6028569333334</v>
+        <v>123.1292677333333</v>
       </c>
       <c r="Q69">
-        <v>181.6028569333334</v>
+        <v>181.1292677333333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1615117273600459</v>
+        <v>0.1648521351937655</v>
       </c>
       <c r="T69">
-        <v>2.255436940372171</v>
+        <v>2.320547706549196</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.895398713059768</v>
+        <v>4.823407555514772</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08283588326200494</v>
+        <v>0.08273209649519474</v>
       </c>
       <c r="C70">
-        <v>467.320431621979</v>
+        <v>459.2130740433294</v>
       </c>
       <c r="D70">
-        <v>924.360431621979</v>
+        <v>926.9580740433296</v>
       </c>
       <c r="E70">
-        <v>350.7400000000001</v>
+        <v>361.4450000000001</v>
       </c>
       <c r="F70">
-        <v>727.9400000000001</v>
+        <v>738.6450000000001</v>
       </c>
       <c r="G70">
         <v>270.9</v>
@@ -7021,28 +7021,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M70">
-        <v>40.255082</v>
+        <v>40.84706850000001</v>
       </c>
       <c r="N70">
-        <v>153.9115846666667</v>
+        <v>153.3195981666667</v>
       </c>
       <c r="O70">
-        <v>30.78231693333333</v>
+        <v>30.66391963333334</v>
       </c>
       <c r="P70">
-        <v>123.1292677333333</v>
+        <v>122.6556785333333</v>
       </c>
       <c r="Q70">
-        <v>181.1292677333333</v>
+        <v>180.6556785333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1648521351937655</v>
+        <v>0.1684080532103056</v>
       </c>
       <c r="T70">
-        <v>2.320547706549196</v>
+        <v>2.389859167318288</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.823407555514772</v>
+        <v>4.75350309818847</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08273209649519474</v>
+        <v>0.08262830972838454</v>
       </c>
       <c r="C71">
-        <v>459.2130740433294</v>
+        <v>451.1203574248667</v>
       </c>
       <c r="D71">
-        <v>926.9580740433296</v>
+        <v>929.5703574248668</v>
       </c>
       <c r="E71">
-        <v>361.4450000000001</v>
+        <v>372.15</v>
       </c>
       <c r="F71">
-        <v>738.6450000000001</v>
+        <v>749.35</v>
       </c>
       <c r="G71">
         <v>270.9</v>
@@ -7103,28 +7103,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M71">
-        <v>40.84706850000001</v>
+        <v>41.439055</v>
       </c>
       <c r="N71">
-        <v>153.3195981666667</v>
+        <v>152.7276116666667</v>
       </c>
       <c r="O71">
-        <v>30.66391963333334</v>
+        <v>30.54552233333334</v>
       </c>
       <c r="P71">
-        <v>122.6556785333333</v>
+        <v>122.1820893333334</v>
       </c>
       <c r="Q71">
-        <v>180.6556785333333</v>
+        <v>180.1820893333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1684080532103056</v>
+        <v>0.1722010324279485</v>
       </c>
       <c r="T71">
-        <v>2.389859167318288</v>
+        <v>2.463791392138653</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.75350309818847</v>
+        <v>4.685595911071492</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08262830972838454</v>
+        <v>0.08252452296157436</v>
       </c>
       <c r="C72">
-        <v>451.1203574248667</v>
+        <v>443.0424058965557</v>
       </c>
       <c r="D72">
-        <v>929.5703574248668</v>
+        <v>932.1974058965557</v>
       </c>
       <c r="E72">
-        <v>372.15</v>
+        <v>382.8550000000001</v>
       </c>
       <c r="F72">
-        <v>749.35</v>
+        <v>760.0550000000001</v>
       </c>
       <c r="G72">
         <v>270.9</v>
@@ -7185,28 +7185,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M72">
-        <v>41.439055</v>
+        <v>42.03104150000001</v>
       </c>
       <c r="N72">
-        <v>152.7276116666667</v>
+        <v>152.1356251666667</v>
       </c>
       <c r="O72">
-        <v>30.54552233333334</v>
+        <v>30.42712503333334</v>
       </c>
       <c r="P72">
-        <v>122.1820893333334</v>
+        <v>121.7085001333333</v>
       </c>
       <c r="Q72">
-        <v>180.1820893333334</v>
+        <v>179.7085001333334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1722010324279485</v>
+        <v>0.1762555964192219</v>
       </c>
       <c r="T72">
-        <v>2.463791392138653</v>
+        <v>2.54282239108456</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.685595911071492</v>
+        <v>4.619601602464851</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08252452296157435</v>
+        <v>0.08242073619476416</v>
       </c>
       <c r="C73">
-        <v>443.0424058965563</v>
+        <v>434.9793449955489</v>
       </c>
       <c r="D73">
-        <v>932.1974058965561</v>
+        <v>934.8393449955489</v>
       </c>
       <c r="E73">
-        <v>382.855</v>
+        <v>393.56</v>
       </c>
       <c r="F73">
-        <v>760.0549999999999</v>
+        <v>770.76</v>
       </c>
       <c r="G73">
         <v>270.9</v>
@@ -7267,28 +7267,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M73">
-        <v>42.0310415</v>
+        <v>42.623028</v>
       </c>
       <c r="N73">
-        <v>152.1356251666667</v>
+        <v>151.5436386666667</v>
       </c>
       <c r="O73">
-        <v>30.42712503333334</v>
+        <v>30.30872773333334</v>
       </c>
       <c r="P73">
-        <v>121.7085001333333</v>
+        <v>121.2349109333333</v>
       </c>
       <c r="Q73">
-        <v>179.7085001333334</v>
+        <v>179.2349109333334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1762555964192219</v>
+        <v>0.1805997721241577</v>
       </c>
       <c r="T73">
-        <v>2.542822391084559</v>
+        <v>2.627498461383745</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.619601602464851</v>
+        <v>4.555440469097285</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08242073619476416</v>
+        <v>0.08377694942795395</v>
       </c>
       <c r="C74">
-        <v>434.9793449955489</v>
+        <v>390.8898444054036</v>
       </c>
       <c r="D74">
-        <v>934.8393449955489</v>
+        <v>901.4548444054037</v>
       </c>
       <c r="E74">
-        <v>393.56</v>
+        <v>404.265</v>
       </c>
       <c r="F74">
-        <v>770.76</v>
+        <v>781.465</v>
       </c>
       <c r="G74">
         <v>270.9</v>
@@ -7349,45 +7349,45 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M74">
-        <v>42.623028</v>
+        <v>45.168677</v>
       </c>
       <c r="N74">
-        <v>151.5436386666667</v>
+        <v>148.9979896666667</v>
       </c>
       <c r="O74">
-        <v>30.30872773333334</v>
+        <v>29.79959793333334</v>
       </c>
       <c r="P74">
-        <v>121.2349109333333</v>
+        <v>119.1983917333334</v>
       </c>
       <c r="Q74">
-        <v>179.2349109333334</v>
+        <v>177.1983917333334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1805997721241577</v>
+        <v>0.1852657386220517</v>
       </c>
       <c r="T74">
-        <v>2.627498461383745</v>
+        <v>2.718446833186575</v>
       </c>
       <c r="U74">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V74">
         <v>0.2</v>
       </c>
       <c r="W74">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.555440469097285</v>
+        <v>4.298701657050231</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08377694942795395</v>
+        <v>0.08369316266114377</v>
       </c>
       <c r="C75">
-        <v>390.8898444054036</v>
+        <v>382.1780796366126</v>
       </c>
       <c r="D75">
-        <v>901.4548444054037</v>
+        <v>903.4480796366124</v>
       </c>
       <c r="E75">
-        <v>404.265</v>
+        <v>414.97</v>
       </c>
       <c r="F75">
-        <v>781.465</v>
+        <v>792.17</v>
       </c>
       <c r="G75">
         <v>270.9</v>
@@ -7431,28 +7431,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M75">
-        <v>45.168677</v>
+        <v>45.787426</v>
       </c>
       <c r="N75">
-        <v>148.9979896666667</v>
+        <v>148.3792406666667</v>
       </c>
       <c r="O75">
-        <v>29.79959793333334</v>
+        <v>29.67584813333334</v>
       </c>
       <c r="P75">
-        <v>119.1983917333334</v>
+        <v>118.7033925333333</v>
       </c>
       <c r="Q75">
-        <v>177.1983917333334</v>
+        <v>176.7033925333334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1852657386220517</v>
+        <v>0.1902906256197837</v>
       </c>
       <c r="T75">
-        <v>2.718446833186575</v>
+        <v>2.816391233589622</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.298701657050231</v>
+        <v>4.24061109411712</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08369316266114377</v>
+        <v>0.08360937589433357</v>
       </c>
       <c r="C76">
-        <v>382.1780796366126</v>
+        <v>373.4751490118165</v>
       </c>
       <c r="D76">
-        <v>903.4480796366124</v>
+        <v>905.4501490118166</v>
       </c>
       <c r="E76">
-        <v>414.97</v>
+        <v>425.675</v>
       </c>
       <c r="F76">
-        <v>792.17</v>
+        <v>802.875</v>
       </c>
       <c r="G76">
         <v>270.9</v>
@@ -7513,28 +7513,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M76">
-        <v>45.787426</v>
+        <v>46.406175</v>
       </c>
       <c r="N76">
-        <v>148.3792406666667</v>
+        <v>147.7604916666667</v>
       </c>
       <c r="O76">
-        <v>29.67584813333334</v>
+        <v>29.55209833333333</v>
       </c>
       <c r="P76">
-        <v>118.7033925333333</v>
+        <v>118.2083933333333</v>
       </c>
       <c r="Q76">
-        <v>176.7033925333334</v>
+        <v>176.2083933333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1902906256197837</v>
+        <v>0.1957175035773343</v>
       </c>
       <c r="T76">
-        <v>2.816391233589622</v>
+        <v>2.922171186024913</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.24061109411712</v>
+        <v>4.184069612862224</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08360937589433357</v>
+        <v>0.08352558912752338</v>
       </c>
       <c r="C77">
-        <v>373.4751490118165</v>
+        <v>364.7811113916765</v>
       </c>
       <c r="D77">
-        <v>905.4501490118166</v>
+        <v>907.4611113916766</v>
       </c>
       <c r="E77">
-        <v>425.675</v>
+        <v>436.3800000000001</v>
       </c>
       <c r="F77">
-        <v>802.875</v>
+        <v>813.58</v>
       </c>
       <c r="G77">
         <v>270.9</v>
@@ -7595,28 +7595,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M77">
-        <v>46.406175</v>
+        <v>47.02492400000001</v>
       </c>
       <c r="N77">
-        <v>147.7604916666667</v>
+        <v>147.1417426666667</v>
       </c>
       <c r="O77">
-        <v>29.55209833333333</v>
+        <v>29.42834853333334</v>
       </c>
       <c r="P77">
-        <v>118.2083933333333</v>
+        <v>117.7133941333334</v>
       </c>
       <c r="Q77">
-        <v>176.2083933333333</v>
+        <v>175.7133941333334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1957175035773343</v>
+        <v>0.2015966213646807</v>
       </c>
       <c r="T77">
-        <v>2.922171186024913</v>
+        <v>3.036766134496479</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.184069612862224</v>
+        <v>4.129016065324564</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08352558912752338</v>
+        <v>0.08344180236071318</v>
       </c>
       <c r="C78">
-        <v>364.7811113916765</v>
+        <v>356.0960261609242</v>
       </c>
       <c r="D78">
-        <v>907.4611113916766</v>
+        <v>909.4810261609242</v>
       </c>
       <c r="E78">
-        <v>436.3800000000001</v>
+        <v>447.085</v>
       </c>
       <c r="F78">
-        <v>813.58</v>
+        <v>824.285</v>
       </c>
       <c r="G78">
         <v>270.9</v>
@@ -7677,28 +7677,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M78">
-        <v>47.02492400000001</v>
+        <v>47.643673</v>
       </c>
       <c r="N78">
-        <v>147.1417426666667</v>
+        <v>146.5229936666667</v>
       </c>
       <c r="O78">
-        <v>29.42834853333334</v>
+        <v>29.30459873333334</v>
       </c>
       <c r="P78">
-        <v>117.7133941333334</v>
+        <v>117.2183949333333</v>
       </c>
       <c r="Q78">
-        <v>175.7133941333334</v>
+        <v>175.2183949333333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2015966213646807</v>
+        <v>0.2079869667857095</v>
       </c>
       <c r="T78">
-        <v>3.036766134496479</v>
+        <v>3.161325861096006</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.129016065324564</v>
+        <v>4.075392480060609</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08344180236071318</v>
+        <v>0.08335801559390298</v>
       </c>
       <c r="C79">
-        <v>356.0960261609242</v>
+        <v>347.419953234207</v>
       </c>
       <c r="D79">
-        <v>909.4810261609242</v>
+        <v>911.5099532342069</v>
       </c>
       <c r="E79">
-        <v>447.085</v>
+        <v>457.79</v>
       </c>
       <c r="F79">
-        <v>824.285</v>
+        <v>834.99</v>
       </c>
       <c r="G79">
         <v>270.9</v>
@@ -7759,28 +7759,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M79">
-        <v>47.643673</v>
+        <v>48.262422</v>
       </c>
       <c r="N79">
-        <v>146.5229936666667</v>
+        <v>145.9042446666667</v>
       </c>
       <c r="O79">
-        <v>29.30459873333334</v>
+        <v>29.18084893333334</v>
       </c>
       <c r="P79">
-        <v>117.2183949333333</v>
+        <v>116.7233957333333</v>
       </c>
       <c r="Q79">
-        <v>175.2183949333333</v>
+        <v>174.7233957333333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2079869667857095</v>
+        <v>0.214958252699559</v>
       </c>
       <c r="T79">
-        <v>3.161325861096006</v>
+        <v>3.297209199204582</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.075392480060609</v>
+        <v>4.023143858521371</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08335801559390298</v>
+        <v>0.08548622882709278</v>
       </c>
       <c r="C80">
-        <v>347.419953234207</v>
+        <v>287.8343313663778</v>
       </c>
       <c r="D80">
-        <v>911.5099532342069</v>
+        <v>862.6293313663779</v>
       </c>
       <c r="E80">
-        <v>457.79</v>
+        <v>468.4950000000001</v>
       </c>
       <c r="F80">
-        <v>834.99</v>
+        <v>845.6950000000001</v>
       </c>
       <c r="G80">
         <v>270.9</v>
@@ -7841,45 +7841,45 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M80">
-        <v>48.262422</v>
+        <v>51.8411035</v>
       </c>
       <c r="N80">
-        <v>145.9042446666667</v>
+        <v>142.3255631666667</v>
       </c>
       <c r="O80">
-        <v>29.18084893333334</v>
+        <v>28.46511263333334</v>
       </c>
       <c r="P80">
-        <v>116.7233957333333</v>
+        <v>113.8604505333333</v>
       </c>
       <c r="Q80">
-        <v>174.7233957333333</v>
+        <v>171.8604505333334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.214958252699559</v>
+        <v>0.2225934706052038</v>
       </c>
       <c r="T80">
-        <v>3.297209199204582</v>
+        <v>3.446033807609212</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.2</v>
       </c>
       <c r="W80">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.023143858521371</v>
+        <v>3.745419243760247</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08548622882709278</v>
+        <v>0.08543044206028258</v>
       </c>
       <c r="C81">
-        <v>287.8343313663778</v>
+        <v>278.3436327682994</v>
       </c>
       <c r="D81">
-        <v>862.6293313663779</v>
+        <v>863.8436327682996</v>
       </c>
       <c r="E81">
-        <v>468.4950000000001</v>
+        <v>479.2000000000001</v>
       </c>
       <c r="F81">
-        <v>845.6950000000001</v>
+        <v>856.4000000000001</v>
       </c>
       <c r="G81">
         <v>270.9</v>
@@ -7923,28 +7923,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M81">
-        <v>51.8411035</v>
+        <v>52.49732000000001</v>
       </c>
       <c r="N81">
-        <v>142.3255631666667</v>
+        <v>141.6693466666667</v>
       </c>
       <c r="O81">
-        <v>28.46511263333334</v>
+        <v>28.33386933333334</v>
       </c>
       <c r="P81">
-        <v>113.8604505333333</v>
+        <v>113.3354773333333</v>
       </c>
       <c r="Q81">
-        <v>171.8604505333334</v>
+        <v>171.3354773333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2225934706052038</v>
+        <v>0.230992210301413</v>
       </c>
       <c r="T81">
-        <v>3.446033807609212</v>
+        <v>3.609740876854306</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.745419243760247</v>
+        <v>3.698601503213243</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08543044206028258</v>
+        <v>0.08537465529347239</v>
       </c>
       <c r="C82">
-        <v>278.3436327682994</v>
+        <v>268.8563576718859</v>
       </c>
       <c r="D82">
-        <v>863.8436327682996</v>
+        <v>865.061357671886</v>
       </c>
       <c r="E82">
-        <v>479.2000000000001</v>
+        <v>489.905</v>
       </c>
       <c r="F82">
-        <v>856.4000000000001</v>
+        <v>867.105</v>
       </c>
       <c r="G82">
         <v>270.9</v>
@@ -8005,28 +8005,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M82">
-        <v>52.49732000000001</v>
+        <v>53.1535365</v>
       </c>
       <c r="N82">
-        <v>141.6693466666667</v>
+        <v>141.0131301666667</v>
       </c>
       <c r="O82">
-        <v>28.33386933333334</v>
+        <v>28.20262603333334</v>
       </c>
       <c r="P82">
-        <v>113.3354773333333</v>
+        <v>112.8105041333334</v>
       </c>
       <c r="Q82">
-        <v>171.3354773333334</v>
+        <v>170.8105041333334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.230992210301413</v>
+        <v>0.2402750278603811</v>
       </c>
       <c r="T82">
-        <v>3.609740876854306</v>
+        <v>3.79068026917783</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.698601503213243</v>
+        <v>3.652939756259994</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08537465529347239</v>
+        <v>0.08531886852666218</v>
       </c>
       <c r="C83">
-        <v>268.8563576718859</v>
+        <v>259.3725205754851</v>
       </c>
       <c r="D83">
-        <v>865.061357671886</v>
+        <v>866.2825205754851</v>
       </c>
       <c r="E83">
-        <v>489.905</v>
+        <v>500.6100000000001</v>
       </c>
       <c r="F83">
-        <v>867.105</v>
+        <v>877.8100000000001</v>
       </c>
       <c r="G83">
         <v>270.9</v>
@@ -8087,28 +8087,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M83">
-        <v>53.1535365</v>
+        <v>53.809753</v>
       </c>
       <c r="N83">
-        <v>141.0131301666667</v>
+        <v>140.3569136666667</v>
       </c>
       <c r="O83">
-        <v>28.20262603333334</v>
+        <v>28.07138273333334</v>
       </c>
       <c r="P83">
-        <v>112.8105041333334</v>
+        <v>112.2855309333333</v>
       </c>
       <c r="Q83">
-        <v>170.8105041333334</v>
+        <v>170.2855309333333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2402750278603811</v>
+        <v>0.2505892695925678</v>
       </c>
       <c r="T83">
-        <v>3.79068026917783</v>
+        <v>3.99172403842619</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.652939756259994</v>
+        <v>3.608391710451945</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08531886852666218</v>
+        <v>0.08526308175985198</v>
       </c>
       <c r="C84">
-        <v>259.3725205754851</v>
+        <v>249.8921360594247</v>
       </c>
       <c r="D84">
-        <v>866.2825205754851</v>
+        <v>867.5071360594249</v>
       </c>
       <c r="E84">
-        <v>500.6100000000001</v>
+        <v>511.3150000000001</v>
       </c>
       <c r="F84">
-        <v>877.8100000000001</v>
+        <v>888.5150000000001</v>
       </c>
       <c r="G84">
         <v>270.9</v>
@@ -8169,28 +8169,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M84">
-        <v>53.809753</v>
+        <v>54.46596950000001</v>
       </c>
       <c r="N84">
-        <v>140.3569136666667</v>
+        <v>139.7006971666667</v>
       </c>
       <c r="O84">
-        <v>28.07138273333334</v>
+        <v>27.94013943333334</v>
       </c>
       <c r="P84">
-        <v>112.2855309333333</v>
+        <v>111.7605577333333</v>
       </c>
       <c r="Q84">
-        <v>170.2855309333333</v>
+        <v>169.7605577333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2505892695925678</v>
+        <v>0.2621169515285412</v>
       </c>
       <c r="T84">
-        <v>3.99172403842619</v>
+        <v>4.216420015821416</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.608391710451945</v>
+        <v>3.564917111530837</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08526308175985198</v>
+        <v>0.0852072949930418</v>
       </c>
       <c r="C85">
-        <v>249.8921360594247</v>
+        <v>240.4152187865963</v>
       </c>
       <c r="D85">
-        <v>867.5071360594249</v>
+        <v>868.7352187865963</v>
       </c>
       <c r="E85">
-        <v>511.3150000000001</v>
+        <v>522.0200000000002</v>
       </c>
       <c r="F85">
-        <v>888.5150000000001</v>
+        <v>899.2200000000001</v>
       </c>
       <c r="G85">
         <v>270.9</v>
@@ -8251,28 +8251,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M85">
-        <v>54.46596950000001</v>
+        <v>55.12218600000001</v>
       </c>
       <c r="N85">
-        <v>139.7006971666667</v>
+        <v>139.0444806666667</v>
       </c>
       <c r="O85">
-        <v>27.94013943333334</v>
+        <v>27.80889613333334</v>
       </c>
       <c r="P85">
-        <v>111.7605577333333</v>
+        <v>111.2355845333334</v>
       </c>
       <c r="Q85">
-        <v>169.7605577333334</v>
+        <v>169.2355845333334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2621169515285412</v>
+        <v>0.2750855937065114</v>
       </c>
       <c r="T85">
-        <v>4.216420015821416</v>
+        <v>4.469202990391047</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.564917111530837</v>
+        <v>3.522477622107851</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0852072949930418</v>
+        <v>0.08705550822623161</v>
       </c>
       <c r="C86">
-        <v>240.4152187865965</v>
+        <v>190.7915871533417</v>
       </c>
       <c r="D86">
-        <v>868.7352187865963</v>
+        <v>829.8165871533415</v>
       </c>
       <c r="E86">
-        <v>522.02</v>
+        <v>532.7249999999999</v>
       </c>
       <c r="F86">
-        <v>899.2199999999999</v>
+        <v>909.925</v>
       </c>
       <c r="G86">
         <v>270.9</v>
@@ -8333,45 +8333,45 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M86">
-        <v>55.12218599999999</v>
+        <v>58.3261925</v>
       </c>
       <c r="N86">
-        <v>139.0444806666667</v>
+        <v>135.8404741666667</v>
       </c>
       <c r="O86">
-        <v>27.80889613333334</v>
+        <v>27.16809483333334</v>
       </c>
       <c r="P86">
-        <v>111.2355845333334</v>
+        <v>108.6723793333334</v>
       </c>
       <c r="Q86">
-        <v>169.2355845333334</v>
+        <v>166.6723793333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2750855937065112</v>
+        <v>0.2897833881748773</v>
       </c>
       <c r="T86">
-        <v>4.469202990391043</v>
+        <v>4.755690361569957</v>
       </c>
       <c r="U86">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V86">
         <v>0.2</v>
       </c>
       <c r="W86">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.522477622107852</v>
+        <v>3.328978943150913</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08705550822623161</v>
+        <v>0.08702212145942141</v>
       </c>
       <c r="C87">
-        <v>190.7915871533417</v>
+        <v>180.7586751466243</v>
       </c>
       <c r="D87">
-        <v>829.8165871533415</v>
+        <v>830.4886751466242</v>
       </c>
       <c r="E87">
-        <v>532.7249999999999</v>
+        <v>543.4300000000001</v>
       </c>
       <c r="F87">
-        <v>909.925</v>
+        <v>920.63</v>
       </c>
       <c r="G87">
         <v>270.9</v>
@@ -8415,28 +8415,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M87">
-        <v>58.3261925</v>
+        <v>59.01238300000001</v>
       </c>
       <c r="N87">
-        <v>135.8404741666667</v>
+        <v>135.1542836666667</v>
       </c>
       <c r="O87">
-        <v>27.16809483333334</v>
+        <v>27.03085673333334</v>
       </c>
       <c r="P87">
-        <v>108.6723793333334</v>
+        <v>108.1234269333333</v>
       </c>
       <c r="Q87">
-        <v>166.6723793333334</v>
+        <v>166.1234269333333</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2897833881748773</v>
+        <v>0.3065808675672957</v>
       </c>
       <c r="T87">
-        <v>4.755690361569957</v>
+        <v>5.083104500060143</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.328978943150913</v>
+        <v>3.290269885672414</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08702212145942141</v>
+        <v>0.0869887346926112</v>
       </c>
       <c r="C88">
-        <v>180.7586751466243</v>
+        <v>170.7268527021515</v>
       </c>
       <c r="D88">
-        <v>830.4886751466242</v>
+        <v>831.1618527021517</v>
       </c>
       <c r="E88">
-        <v>543.4300000000001</v>
+        <v>554.135</v>
       </c>
       <c r="F88">
-        <v>920.63</v>
+        <v>931.335</v>
       </c>
       <c r="G88">
         <v>270.9</v>
@@ -8497,28 +8497,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M88">
-        <v>59.01238300000001</v>
+        <v>59.69857350000001</v>
       </c>
       <c r="N88">
-        <v>135.1542836666667</v>
+        <v>134.4680931666667</v>
       </c>
       <c r="O88">
-        <v>27.03085673333334</v>
+        <v>26.89361863333334</v>
       </c>
       <c r="P88">
-        <v>108.1234269333333</v>
+        <v>107.5744745333333</v>
       </c>
       <c r="Q88">
-        <v>166.1234269333333</v>
+        <v>165.5744745333334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3065808675672957</v>
+        <v>0.3259625745585477</v>
       </c>
       <c r="T88">
-        <v>5.083104500060143</v>
+        <v>5.460890044471896</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.290269885672414</v>
+        <v>3.252450691584225</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.0869887346926112</v>
+        <v>0.08695534792580102</v>
       </c>
       <c r="C89">
-        <v>170.7268527021515</v>
+        <v>160.6961224716047</v>
       </c>
       <c r="D89">
-        <v>831.1618527021517</v>
+        <v>831.8361224716045</v>
       </c>
       <c r="E89">
-        <v>554.135</v>
+        <v>564.8399999999999</v>
       </c>
       <c r="F89">
-        <v>931.335</v>
+        <v>942.04</v>
       </c>
       <c r="G89">
         <v>270.9</v>
@@ -8579,28 +8579,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M89">
-        <v>59.69857350000001</v>
+        <v>60.384764</v>
       </c>
       <c r="N89">
-        <v>134.4680931666667</v>
+        <v>133.7819026666667</v>
       </c>
       <c r="O89">
-        <v>26.89361863333334</v>
+        <v>26.75638053333333</v>
       </c>
       <c r="P89">
-        <v>107.5744745333333</v>
+        <v>107.0255221333333</v>
       </c>
       <c r="Q89">
-        <v>165.5744745333334</v>
+        <v>165.0255221333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3259625745585477</v>
+        <v>0.3485745660483418</v>
       </c>
       <c r="T89">
-        <v>5.460890044471896</v>
+        <v>5.90163984628561</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.252450691584225</v>
+        <v>3.215491024634404</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08695534792580102</v>
+        <v>0.08692196115899081</v>
       </c>
       <c r="C90">
-        <v>160.6961224716047</v>
+        <v>150.6664871152774</v>
       </c>
       <c r="D90">
-        <v>831.8361224716045</v>
+        <v>832.5114871152773</v>
       </c>
       <c r="E90">
-        <v>564.8399999999999</v>
+        <v>575.5450000000001</v>
       </c>
       <c r="F90">
-        <v>942.04</v>
+        <v>952.745</v>
       </c>
       <c r="G90">
         <v>270.9</v>
@@ -8661,28 +8661,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M90">
-        <v>60.384764</v>
+        <v>61.07095450000001</v>
       </c>
       <c r="N90">
-        <v>133.7819026666667</v>
+        <v>133.0957121666667</v>
       </c>
       <c r="O90">
-        <v>26.75638053333333</v>
+        <v>26.61914243333334</v>
       </c>
       <c r="P90">
-        <v>107.0255221333333</v>
+        <v>106.4765697333333</v>
       </c>
       <c r="Q90">
-        <v>165.0255221333334</v>
+        <v>164.4765697333333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3485745660483418</v>
+        <v>0.3752978287180984</v>
       </c>
       <c r="T90">
-        <v>5.90163984628561</v>
+        <v>6.422525975701816</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.215491024634404</v>
+        <v>3.179361911998063</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08692196115899081</v>
+        <v>0.08688857439218062</v>
       </c>
       <c r="C91">
-        <v>150.6664871152774</v>
+        <v>140.6379493021088</v>
       </c>
       <c r="D91">
-        <v>832.5114871152773</v>
+        <v>833.1879493021089</v>
       </c>
       <c r="E91">
-        <v>575.5450000000001</v>
+        <v>586.25</v>
       </c>
       <c r="F91">
-        <v>952.745</v>
+        <v>963.45</v>
       </c>
       <c r="G91">
         <v>270.9</v>
@@ -8743,28 +8743,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M91">
-        <v>61.07095450000001</v>
+        <v>61.75714500000001</v>
       </c>
       <c r="N91">
-        <v>133.0957121666667</v>
+        <v>132.4095216666667</v>
       </c>
       <c r="O91">
-        <v>26.61914243333334</v>
+        <v>26.48190433333334</v>
       </c>
       <c r="P91">
-        <v>106.4765697333333</v>
+        <v>105.9276173333333</v>
       </c>
       <c r="Q91">
-        <v>164.4765697333333</v>
+        <v>163.9276173333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3752978287180984</v>
+        <v>0.4073657439218063</v>
       </c>
       <c r="T91">
-        <v>6.422525975701816</v>
+        <v>7.047589331001264</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.179361911998063</v>
+        <v>3.144035668531417</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08688857439218062</v>
+        <v>0.08685518762537042</v>
       </c>
       <c r="C92">
-        <v>140.6379493021088</v>
+        <v>130.610511709721</v>
       </c>
       <c r="D92">
-        <v>833.1879493021089</v>
+        <v>833.8655117097212</v>
       </c>
       <c r="E92">
-        <v>586.25</v>
+        <v>596.9550000000002</v>
       </c>
       <c r="F92">
-        <v>963.45</v>
+        <v>974.1550000000001</v>
       </c>
       <c r="G92">
         <v>270.9</v>
@@ -8825,28 +8825,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M92">
-        <v>61.75714500000001</v>
+        <v>62.44333550000001</v>
       </c>
       <c r="N92">
-        <v>132.4095216666667</v>
+        <v>131.7233311666667</v>
       </c>
       <c r="O92">
-        <v>26.48190433333334</v>
+        <v>26.34466623333334</v>
       </c>
       <c r="P92">
-        <v>105.9276173333333</v>
+        <v>105.3786649333333</v>
       </c>
       <c r="Q92">
-        <v>163.9276173333334</v>
+        <v>163.3786649333334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4073657439218063</v>
+        <v>0.4465598625041159</v>
       </c>
       <c r="T92">
-        <v>7.047589331001264</v>
+        <v>7.811555654145033</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.144035668531417</v>
+        <v>3.109485826020082</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08685518762537042</v>
+        <v>0.08682180085856023</v>
       </c>
       <c r="C93">
-        <v>130.610511709721</v>
+        <v>120.5841770244525</v>
       </c>
       <c r="D93">
-        <v>833.8655117097212</v>
+        <v>834.5441770244524</v>
       </c>
       <c r="E93">
-        <v>596.9550000000002</v>
+        <v>607.6600000000001</v>
       </c>
       <c r="F93">
-        <v>974.1550000000001</v>
+        <v>984.86</v>
       </c>
       <c r="G93">
         <v>270.9</v>
@@ -8907,28 +8907,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M93">
-        <v>62.44333550000001</v>
+        <v>63.12952600000001</v>
       </c>
       <c r="N93">
-        <v>131.7233311666667</v>
+        <v>131.0371406666667</v>
       </c>
       <c r="O93">
-        <v>26.34466623333334</v>
+        <v>26.20742813333334</v>
       </c>
       <c r="P93">
-        <v>105.3786649333333</v>
+        <v>104.8297125333333</v>
       </c>
       <c r="Q93">
-        <v>163.3786649333334</v>
+        <v>162.8297125333333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4465598625041159</v>
+        <v>0.4955525107320031</v>
       </c>
       <c r="T93">
-        <v>7.811555654145033</v>
+        <v>8.766513558074745</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.109485826020082</v>
+        <v>3.075687067041604</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08682180085856023</v>
+        <v>0.08678841409175003</v>
       </c>
       <c r="C94">
-        <v>120.5841770244525</v>
+        <v>110.5589479413936</v>
       </c>
       <c r="D94">
-        <v>834.5441770244524</v>
+        <v>835.2239479413937</v>
       </c>
       <c r="E94">
-        <v>607.6600000000001</v>
+        <v>618.365</v>
       </c>
       <c r="F94">
-        <v>984.86</v>
+        <v>995.5650000000001</v>
       </c>
       <c r="G94">
         <v>270.9</v>
@@ -8989,28 +8989,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M94">
-        <v>63.12952600000001</v>
+        <v>63.81571650000001</v>
       </c>
       <c r="N94">
-        <v>131.0371406666667</v>
+        <v>130.3509501666667</v>
       </c>
       <c r="O94">
-        <v>26.20742813333334</v>
+        <v>26.07019003333334</v>
       </c>
       <c r="P94">
-        <v>104.8297125333333</v>
+        <v>104.2807601333333</v>
       </c>
       <c r="Q94">
-        <v>162.8297125333333</v>
+        <v>162.2807601333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4955525107320031</v>
+        <v>0.5585430584535721</v>
       </c>
       <c r="T94">
-        <v>8.766513558074745</v>
+        <v>9.994316577412945</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.075687067041604</v>
+        <v>3.04261516309492</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08678841409175003</v>
+        <v>0.08675502732493984</v>
       </c>
       <c r="C95">
-        <v>110.5589479413936</v>
+        <v>100.5348271644242</v>
       </c>
       <c r="D95">
-        <v>835.2239479413937</v>
+        <v>835.9048271644244</v>
       </c>
       <c r="E95">
-        <v>618.365</v>
+        <v>629.0700000000002</v>
       </c>
       <c r="F95">
-        <v>995.5650000000001</v>
+        <v>1006.27</v>
       </c>
       <c r="G95">
         <v>270.9</v>
@@ -9071,28 +9071,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M95">
-        <v>63.81571650000001</v>
+        <v>64.50190700000002</v>
       </c>
       <c r="N95">
-        <v>130.3509501666667</v>
+        <v>129.6647596666667</v>
       </c>
       <c r="O95">
-        <v>26.07019003333334</v>
+        <v>25.93295193333334</v>
       </c>
       <c r="P95">
-        <v>104.2807601333333</v>
+        <v>103.7318077333333</v>
       </c>
       <c r="Q95">
-        <v>162.2807601333334</v>
+        <v>161.7318077333334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5585430584535721</v>
+        <v>0.6425304554156643</v>
       </c>
       <c r="T95">
-        <v>9.994316577412945</v>
+        <v>11.63138726986388</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.04261516309492</v>
+        <v>3.010246916679016</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08675502732493984</v>
+        <v>0.09264964055812965</v>
       </c>
       <c r="C96">
-        <v>100.5348271644242</v>
+        <v>-15.34356578353129</v>
       </c>
       <c r="D96">
-        <v>835.9048271644244</v>
+        <v>730.7314342164688</v>
       </c>
       <c r="E96">
-        <v>629.0700000000002</v>
+        <v>639.7750000000001</v>
       </c>
       <c r="F96">
-        <v>1006.27</v>
+        <v>1016.975</v>
       </c>
       <c r="G96">
         <v>270.9</v>
@@ -9153,45 +9153,45 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M96">
-        <v>64.50190700000002</v>
+        <v>73.1205025</v>
       </c>
       <c r="N96">
-        <v>129.6647596666667</v>
+        <v>121.0461641666667</v>
       </c>
       <c r="O96">
-        <v>25.93295193333334</v>
+        <v>24.20923283333334</v>
       </c>
       <c r="P96">
-        <v>103.7318077333333</v>
+        <v>96.83693133333335</v>
       </c>
       <c r="Q96">
-        <v>161.7318077333334</v>
+        <v>154.8369313333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6425304554156643</v>
+        <v>0.7601128111625937</v>
       </c>
       <c r="T96">
-        <v>11.63138726986388</v>
+        <v>13.9232862392952</v>
       </c>
       <c r="U96">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V96">
         <v>0.2</v>
       </c>
       <c r="W96">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.010246916679016</v>
+        <v>2.655433975808176</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09264964055812965</v>
+        <v>0.09267865379131944</v>
       </c>
       <c r="C97">
-        <v>-15.34356578353129</v>
+        <v>-26.50081600373642</v>
       </c>
       <c r="D97">
-        <v>730.7314342164688</v>
+        <v>730.2791839962637</v>
       </c>
       <c r="E97">
-        <v>639.7750000000001</v>
+        <v>650.48</v>
       </c>
       <c r="F97">
-        <v>1016.975</v>
+        <v>1027.68</v>
       </c>
       <c r="G97">
         <v>270.9</v>
@@ -9235,28 +9235,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M97">
-        <v>73.1205025</v>
+        <v>73.89019200000001</v>
       </c>
       <c r="N97">
-        <v>121.0461641666667</v>
+        <v>120.2764746666667</v>
       </c>
       <c r="O97">
-        <v>24.20923283333334</v>
+        <v>24.05529493333334</v>
       </c>
       <c r="P97">
-        <v>96.83693133333335</v>
+        <v>96.22117973333334</v>
       </c>
       <c r="Q97">
-        <v>154.8369313333334</v>
+        <v>154.2211797333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7601128111625937</v>
+        <v>0.9364863447829875</v>
       </c>
       <c r="T97">
-        <v>13.9232862392952</v>
+        <v>17.36113469344216</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.655433975808176</v>
+        <v>2.62777320522684</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09267865379131944</v>
+        <v>0.09270766702450925</v>
       </c>
       <c r="C98">
-        <v>-26.50081600373642</v>
+        <v>-37.65750677419987</v>
       </c>
       <c r="D98">
-        <v>730.2791839962637</v>
+        <v>729.8274932258001</v>
       </c>
       <c r="E98">
-        <v>650.48</v>
+        <v>661.1849999999999</v>
       </c>
       <c r="F98">
-        <v>1027.68</v>
+        <v>1038.385</v>
       </c>
       <c r="G98">
         <v>270.9</v>
@@ -9317,28 +9317,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M98">
-        <v>73.89019200000001</v>
+        <v>74.65988150000001</v>
       </c>
       <c r="N98">
-        <v>120.2764746666667</v>
+        <v>119.5067851666667</v>
       </c>
       <c r="O98">
-        <v>24.05529493333334</v>
+        <v>23.90135703333334</v>
       </c>
       <c r="P98">
-        <v>96.22117973333334</v>
+        <v>95.60542813333333</v>
       </c>
       <c r="Q98">
-        <v>154.2211797333334</v>
+        <v>153.6054281333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9364863447829851</v>
+        <v>1.230442234150307</v>
       </c>
       <c r="T98">
-        <v>17.36113469344212</v>
+        <v>23.09088211702037</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.62777320522684</v>
+        <v>2.600682759812131</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09270766702450925</v>
+        <v>0.09273668025769904</v>
       </c>
       <c r="C99">
-        <v>-37.65750677419987</v>
+        <v>-48.81363913236873</v>
       </c>
       <c r="D99">
-        <v>729.8274932258001</v>
+        <v>729.3763608676312</v>
       </c>
       <c r="E99">
-        <v>661.1849999999999</v>
+        <v>671.8899999999999</v>
       </c>
       <c r="F99">
-        <v>1038.385</v>
+        <v>1049.09</v>
       </c>
       <c r="G99">
         <v>270.9</v>
@@ -9399,28 +9399,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M99">
-        <v>74.65988150000001</v>
+        <v>75.429571</v>
       </c>
       <c r="N99">
-        <v>119.5067851666667</v>
+        <v>118.7370956666667</v>
       </c>
       <c r="O99">
-        <v>23.90135703333334</v>
+        <v>23.74741913333334</v>
       </c>
       <c r="P99">
-        <v>95.60542813333333</v>
+        <v>94.98967653333335</v>
       </c>
       <c r="Q99">
-        <v>153.6054281333334</v>
+        <v>152.9896765333334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.230442234150307</v>
+        <v>1.81835401288495</v>
       </c>
       <c r="T99">
-        <v>23.09088211702037</v>
+        <v>34.55037696417688</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.600682759812131</v>
+        <v>2.574145180630375</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09273668025769904</v>
+        <v>0.09276569349088885</v>
       </c>
       <c r="C100">
-        <v>-48.81363913236873</v>
+        <v>-59.96921411312792</v>
       </c>
       <c r="D100">
-        <v>729.3763608676312</v>
+        <v>728.9257858868722</v>
       </c>
       <c r="E100">
-        <v>671.8899999999999</v>
+        <v>682.595</v>
       </c>
       <c r="F100">
-        <v>1049.09</v>
+        <v>1059.795</v>
       </c>
       <c r="G100">
         <v>270.9</v>
@@ -9481,28 +9481,28 @@
         <v>194.1666666666667</v>
       </c>
       <c r="M100">
-        <v>75.429571</v>
+        <v>76.19926050000001</v>
       </c>
       <c r="N100">
-        <v>118.7370956666667</v>
+        <v>117.9674061666667</v>
       </c>
       <c r="O100">
-        <v>23.74741913333334</v>
+        <v>23.59348123333334</v>
       </c>
       <c r="P100">
-        <v>94.98967653333335</v>
+        <v>94.37392493333334</v>
       </c>
       <c r="Q100">
-        <v>152.9896765333334</v>
+        <v>152.3739249333333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.81835401288495</v>
+        <v>3.582089349088881</v>
       </c>
       <c r="T100">
-        <v>34.55037696417688</v>
+        <v>68.92886150564642</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.574145180630375</v>
+        <v>2.548143714159361</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09276569349088885</v>
-      </c>
-      <c r="C101">
-        <v>-59.96921411312792</v>
-      </c>
-      <c r="D101">
-        <v>728.9257858868722</v>
-      </c>
-      <c r="E101">
-        <v>682.595</v>
-      </c>
-      <c r="F101">
-        <v>1059.795</v>
-      </c>
-      <c r="G101">
-        <v>270.9</v>
-      </c>
-      <c r="H101">
-        <v>693.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>252.1666666666667</v>
-      </c>
-      <c r="K101">
-        <v>58.00000000000001</v>
-      </c>
-      <c r="L101">
-        <v>194.1666666666667</v>
-      </c>
-      <c r="M101">
-        <v>76.19926050000001</v>
-      </c>
-      <c r="N101">
-        <v>117.9674061666667</v>
-      </c>
-      <c r="O101">
-        <v>23.59348123333334</v>
-      </c>
-      <c r="P101">
-        <v>94.37392493333334</v>
-      </c>
-      <c r="Q101">
-        <v>152.3739249333333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.582089349088881</v>
-      </c>
-      <c r="T101">
-        <v>68.92886150564642</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.05752000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.548143714159361</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
